--- a/jogos_2025-08-24.xlsx
+++ b/jogos_2025-08-24.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tatung</t>
+          <t>Ming Chuan University</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tainan City</t>
+          <t>Hang Yuen FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ming Chuan University</t>
+          <t>Tatung</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hang Yuen FC</t>
+          <t>Tainan City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,22 +2627,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2768,22 +2768,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3827,10 +3827,10 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3968,10 +3968,10 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Taipower</t>
+          <t>Taichung Rock</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AC Taipei</t>
+          <t>Taichung Futuro</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4178,22 +4178,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4397,10 +4397,10 @@
         <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -4460,22 +4460,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Taiwan Taiwan Football Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Taichung Rock</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Taichung Futuro</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4742,22 +4742,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4883,22 +4883,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5060,13 +5060,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5102,10 +5102,10 @@
         <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Taiwan Taiwan Football Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Taipower</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>AC Taipei</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5588,22 +5588,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5660,10 +5660,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z37" t="n">
         <v>0</v>
@@ -5729,22 +5729,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5870,22 +5870,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6047,13 +6047,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -6083,10 +6083,10 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7290,12 +7290,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Isloch</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Vitebsk</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Isloch</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitebsk</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7703,22 +7703,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7844,22 +7844,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7995,12 +7995,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8126,22 +8126,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8267,22 +8267,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8972,22 +8972,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9008,13 +9008,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -9050,10 +9050,10 @@
         <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
         <v>0</v>
@@ -9123,12 +9123,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9149,10 +9149,10 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="M62" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="N62" t="n">
         <v>5.2</v>
@@ -9185,16 +9185,16 @@
         <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB62" t="n">
         <v>0</v>
@@ -9254,22 +9254,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9431,13 +9431,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -9467,10 +9467,10 @@
         <v>0</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Z64" t="n">
         <v>0</v>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9828,12 +9828,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9969,12 +9969,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -10100,22 +10100,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -10277,13 +10277,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -10313,10 +10313,10 @@
         <v>0</v>
       </c>
       <c r="X70" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z70" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -10418,13 +10418,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -10454,10 +10454,10 @@
         <v>0</v>
       </c>
       <c r="X71" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
         <v>0</v>
@@ -10523,22 +10523,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10559,13 +10559,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -10595,10 +10595,10 @@
         <v>0</v>
       </c>
       <c r="X72" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z72" t="n">
         <v>0</v>
@@ -10664,22 +10664,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10805,22 +10805,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10877,10 +10877,10 @@
         <v>0</v>
       </c>
       <c r="X74" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z74" t="n">
         <v>0</v>
@@ -11228,7 +11228,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -11238,12 +11238,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -11264,13 +11264,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -11369,22 +11369,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>UNA Strassen</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -11520,12 +11520,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -11542,7 +11542,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L79" t="n">
@@ -11802,12 +11802,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11933,7 +11933,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11943,12 +11943,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -12084,12 +12084,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -12215,22 +12215,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -12356,7 +12356,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Slutsk</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Neman Grodno</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -12497,22 +12497,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -12638,7 +12638,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -12648,12 +12648,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>UN Käerjéng</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12779,7 +12779,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12789,12 +12789,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12920,7 +12920,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12930,12 +12930,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -13061,7 +13061,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -13071,12 +13071,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -13202,7 +13202,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -13212,12 +13212,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -13234,7 +13234,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L91" t="n">
@@ -13343,22 +13343,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>UNA Strassen</t>
+          <t>Slutsk</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>Neman Grodno</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -13484,7 +13484,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -13494,12 +13494,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>UN Käerjéng</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -13520,13 +13520,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -13625,22 +13625,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -13766,22 +13766,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13917,12 +13917,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -14261,10 +14261,10 @@
         <v>0</v>
       </c>
       <c r="X98" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z98" t="n">
         <v>0</v>
@@ -14471,22 +14471,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -14507,13 +14507,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -14543,10 +14543,10 @@
         <v>0</v>
       </c>
       <c r="X100" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z100" t="n">
         <v>0</v>
@@ -14612,22 +14612,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -14763,12 +14763,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -15176,22 +15176,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -15317,7 +15317,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -15353,13 +15353,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -15389,10 +15389,10 @@
         <v>0</v>
       </c>
       <c r="X106" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z106" t="n">
         <v>0</v>
@@ -15458,7 +15458,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -15468,12 +15468,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -15599,7 +15599,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -15609,12 +15609,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -15740,7 +15740,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -15750,12 +15750,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -15772,7 +15772,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L109" t="n">
@@ -15881,22 +15881,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -16022,7 +16022,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -16032,12 +16032,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -16173,12 +16173,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -16195,7 +16195,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L112" t="n">
@@ -16304,7 +16304,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -16314,12 +16314,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -16455,12 +16455,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -16586,7 +16586,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -16596,12 +16596,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -16618,7 +16618,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L115" t="n">
@@ -16727,7 +16727,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -16737,12 +16737,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -16878,12 +16878,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -17009,7 +17009,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -17019,12 +17019,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -17041,7 +17041,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L118" t="n">
@@ -17150,7 +17150,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -17160,12 +17160,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -17301,12 +17301,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -17323,7 +17323,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L120" t="n">
@@ -17432,22 +17432,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -17464,17 +17464,17 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -17504,10 +17504,10 @@
         <v>0</v>
       </c>
       <c r="X121" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Y121" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z121" t="n">
         <v>0</v>
@@ -17573,22 +17573,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -17609,13 +17609,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -17645,10 +17645,10 @@
         <v>0</v>
       </c>
       <c r="X122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y122" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z122" t="n">
         <v>0</v>
@@ -17714,7 +17714,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -17724,12 +17724,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -17786,10 +17786,10 @@
         <v>0</v>
       </c>
       <c r="X123" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Y123" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z123" t="n">
         <v>0</v>
@@ -17855,7 +17855,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -17891,13 +17891,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -17927,10 +17927,10 @@
         <v>0</v>
       </c>
       <c r="X124" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z124" t="n">
         <v>0</v>
@@ -17996,22 +17996,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -18028,7 +18028,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L125" t="n">
@@ -18137,7 +18137,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -18147,12 +18147,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -18278,7 +18278,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -18288,12 +18288,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -18310,7 +18310,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L127" t="n">
@@ -18419,7 +18419,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -18429,12 +18429,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -18570,12 +18570,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -18701,7 +18701,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -18711,12 +18711,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -18842,7 +18842,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -18852,12 +18852,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -18874,7 +18874,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L131" t="n">
@@ -18983,7 +18983,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -18993,12 +18993,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -19265,7 +19265,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -19406,7 +19406,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -19416,12 +19416,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -19547,7 +19547,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -19557,12 +19557,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ironi Ramat HaSharon</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -19688,7 +19688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -19698,12 +19698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -19839,12 +19839,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -19970,22 +19970,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -20262,12 +20262,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Komárno</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Spartak Trnava</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -20403,12 +20403,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -20534,7 +20534,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -20544,12 +20544,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -20566,7 +20566,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L143" t="n">
@@ -20675,7 +20675,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -20685,12 +20685,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -20711,13 +20711,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M144" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -20747,10 +20747,10 @@
         <v>0</v>
       </c>
       <c r="X144" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y144" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z144" t="n">
         <v>0</v>
@@ -20816,7 +20816,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -20826,12 +20826,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -20957,7 +20957,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -20967,12 +20967,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -21098,7 +21098,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -21108,12 +21108,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Ironi Ramat HaSharon</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -21239,7 +21239,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -21249,12 +21249,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -21275,13 +21275,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M148" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N148" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -21311,10 +21311,10 @@
         <v>0</v>
       </c>
       <c r="X148" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Y148" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z148" t="n">
         <v>0</v>
@@ -21380,7 +21380,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -21390,12 +21390,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -21416,13 +21416,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M149" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N149" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -21452,10 +21452,10 @@
         <v>0</v>
       </c>
       <c r="X149" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Y149" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z149" t="n">
         <v>0</v>
@@ -21521,7 +21521,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -21531,12 +21531,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -21662,7 +21662,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -21672,12 +21672,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -21803,7 +21803,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -21813,12 +21813,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -21944,7 +21944,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -21954,12 +21954,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -22085,7 +22085,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -22095,12 +22095,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -22121,13 +22121,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M154" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N154" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -22157,10 +22157,10 @@
         <v>0</v>
       </c>
       <c r="X154" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y154" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z154" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -22367,7 +22367,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -22377,12 +22377,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -22403,13 +22403,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="M156" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N156" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -22439,10 +22439,10 @@
         <v>0</v>
       </c>
       <c r="X156" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Y156" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z156" t="n">
         <v>0</v>
@@ -22508,7 +22508,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -22518,12 +22518,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Komárno</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Spartak Trnava</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -22659,12 +22659,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -22800,12 +22800,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -22941,12 +22941,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -23354,7 +23354,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -23364,12 +23364,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -23390,13 +23390,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>1.55</v>
+        <v>2.8</v>
       </c>
       <c r="M163" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N163" t="n">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -23426,10 +23426,10 @@
         <v>0</v>
       </c>
       <c r="X163" t="n">
-        <v>1.96</v>
+        <v>1.69</v>
       </c>
       <c r="Y163" t="n">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="Z163" t="n">
         <v>0</v>
@@ -23495,7 +23495,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -23505,12 +23505,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -23636,7 +23636,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -23646,12 +23646,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -23672,13 +23672,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="M165" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="N165" t="n">
-        <v>3.45</v>
+        <v>5.4</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -23708,16 +23708,16 @@
         <v>0</v>
       </c>
       <c r="X165" t="n">
-        <v>1.55</v>
+        <v>1.96</v>
       </c>
       <c r="Y165" t="n">
-        <v>2.4</v>
+        <v>1.75</v>
       </c>
       <c r="Z165" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA165" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB165" t="n">
         <v>0</v>
@@ -23777,7 +23777,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -23787,12 +23787,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -23918,7 +23918,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -23928,12 +23928,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -24059,7 +24059,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -24069,12 +24069,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -24200,7 +24200,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -24210,12 +24210,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -24341,7 +24341,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -24351,12 +24351,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -24377,52 +24377,52 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>2.8</v>
+        <v>1.83</v>
       </c>
       <c r="M170" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N170" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O170" t="n">
+        <v>0</v>
+      </c>
+      <c r="P170" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>0</v>
+      </c>
+      <c r="R170" t="n">
+        <v>0</v>
+      </c>
+      <c r="S170" t="n">
+        <v>0</v>
+      </c>
+      <c r="T170" t="n">
+        <v>0</v>
+      </c>
+      <c r="U170" t="n">
+        <v>0</v>
+      </c>
+      <c r="V170" t="n">
+        <v>0</v>
+      </c>
+      <c r="W170" t="n">
+        <v>0</v>
+      </c>
+      <c r="X170" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Y170" t="n">
         <v>2.4</v>
       </c>
-      <c r="O170" t="n">
-        <v>0</v>
-      </c>
-      <c r="P170" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
-      <c r="R170" t="n">
-        <v>0</v>
-      </c>
-      <c r="S170" t="n">
-        <v>0</v>
-      </c>
-      <c r="T170" t="n">
-        <v>0</v>
-      </c>
-      <c r="U170" t="n">
-        <v>0</v>
-      </c>
-      <c r="V170" t="n">
-        <v>0</v>
-      </c>
-      <c r="W170" t="n">
-        <v>0</v>
-      </c>
-      <c r="X170" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Y170" t="n">
-        <v>2.17</v>
-      </c>
       <c r="Z170" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA170" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB170" t="n">
         <v>0</v>
@@ -24482,7 +24482,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -24492,12 +24492,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -24623,7 +24623,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -24633,12 +24633,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -24905,22 +24905,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -25046,7 +25046,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -25056,12 +25056,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -25187,7 +25187,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -25197,12 +25197,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -25328,22 +25328,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -25469,7 +25469,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -25479,12 +25479,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -25610,22 +25610,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -25751,7 +25751,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -25761,12 +25761,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -25892,7 +25892,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -25902,12 +25902,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -26033,22 +26033,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -26174,7 +26174,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -26184,12 +26184,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -26315,7 +26315,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -26325,12 +26325,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -26456,7 +26456,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -26466,12 +26466,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -26597,22 +26597,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -26738,22 +26738,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -26879,7 +26879,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -26889,12 +26889,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -27020,7 +27020,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -27030,12 +27030,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -27161,22 +27161,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -27302,7 +27302,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -27312,12 +27312,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -27443,7 +27443,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -27453,12 +27453,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -27584,7 +27584,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -27594,12 +27594,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -27725,7 +27725,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -27735,12 +27735,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -27876,12 +27876,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -28007,7 +28007,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -28017,12 +28017,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -28148,7 +28148,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -28158,12 +28158,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -28289,7 +28289,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -28299,12 +28299,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -28430,7 +28430,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -28440,12 +28440,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -28571,7 +28571,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -28581,12 +28581,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -28712,22 +28712,22 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -28853,7 +28853,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -28863,12 +28863,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -29004,12 +29004,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -29135,22 +29135,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -29276,22 +29276,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -29417,7 +29417,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -29427,12 +29427,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -29558,7 +29558,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -29568,12 +29568,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -29594,13 +29594,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M207" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N207" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -29630,10 +29630,10 @@
         <v>0</v>
       </c>
       <c r="X207" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Y207" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z207" t="n">
         <v>0</v>
@@ -29699,7 +29699,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -29709,12 +29709,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -29850,12 +29850,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -29876,13 +29876,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>3.15</v>
+        <v>2.55</v>
       </c>
       <c r="M209" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N209" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -29912,10 +29912,10 @@
         <v>0</v>
       </c>
       <c r="X209" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="Y209" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="Z209" t="n">
         <v>0</v>
@@ -30122,7 +30122,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -30132,12 +30132,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -30158,13 +30158,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M211" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N211" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -30194,10 +30194,10 @@
         <v>0</v>
       </c>
       <c r="X211" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y211" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z211" t="n">
         <v>0</v>
@@ -30263,7 +30263,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -30273,12 +30273,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -30545,7 +30545,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -30555,12 +30555,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -30686,7 +30686,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -30696,12 +30696,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Podbrezová</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -30827,7 +30827,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -30837,12 +30837,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Podbrezová</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -30968,22 +30968,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -31119,12 +31119,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -31260,12 +31260,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -31401,12 +31401,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -31532,22 +31532,22 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Kolkheti Poti</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -31673,7 +31673,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -31683,12 +31683,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -31814,7 +31814,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -31824,12 +31824,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -32096,22 +32096,22 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Kolkheti Poti</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -32237,22 +32237,22 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -32378,22 +32378,22 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -32414,13 +32414,13 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M227" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N227" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -32450,10 +32450,10 @@
         <v>0</v>
       </c>
       <c r="X227" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Y227" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Z227" t="n">
         <v>0</v>
@@ -32660,7 +32660,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -32670,12 +32670,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -32696,13 +32696,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M229" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N229" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -32732,10 +32732,10 @@
         <v>0</v>
       </c>
       <c r="X229" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Y229" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Z229" t="n">
         <v>0</v>
@@ -32801,22 +32801,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -32942,7 +32942,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -32952,12 +32952,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -33083,7 +33083,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -33093,12 +33093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -33224,7 +33224,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -33234,12 +33234,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -33365,7 +33365,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -33375,12 +33375,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -33506,7 +33506,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -33516,12 +33516,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -33647,7 +33647,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -33657,12 +33657,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -33683,13 +33683,13 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="M236" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="N236" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="O236" t="n">
         <v>0</v>
@@ -33719,10 +33719,10 @@
         <v>0</v>
       </c>
       <c r="X236" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Y236" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Z236" t="n">
         <v>0</v>
@@ -33788,7 +33788,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -33798,12 +33798,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -33824,13 +33824,13 @@
         </is>
       </c>
       <c r="L237" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="M237" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="N237" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="O237" t="n">
         <v>0</v>
@@ -33860,10 +33860,10 @@
         <v>0</v>
       </c>
       <c r="X237" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Y237" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Z237" t="n">
         <v>0</v>
@@ -33929,22 +33929,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -34352,22 +34352,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -34926,12 +34926,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -35067,12 +35067,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -35198,7 +35198,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -35208,12 +35208,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -35234,13 +35234,13 @@
         </is>
       </c>
       <c r="L247" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M247" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N247" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O247" t="n">
         <v>0</v>
@@ -35270,10 +35270,10 @@
         <v>0</v>
       </c>
       <c r="X247" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Y247" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z247" t="n">
         <v>0</v>
@@ -35339,22 +35339,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -35490,12 +35490,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -35621,22 +35621,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -35762,7 +35762,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -35772,12 +35772,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -35798,13 +35798,13 @@
         </is>
       </c>
       <c r="L251" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M251" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N251" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O251" t="n">
         <v>0</v>
@@ -35834,10 +35834,10 @@
         <v>0</v>
       </c>
       <c r="X251" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Y251" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z251" t="n">
         <v>0</v>
@@ -35913,12 +35913,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -36054,12 +36054,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -36608,22 +36608,22 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -36749,22 +36749,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -37172,22 +37172,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -37313,22 +37313,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -37349,13 +37349,13 @@
         </is>
       </c>
       <c r="L262" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M262" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N262" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O262" t="n">
         <v>0</v>
@@ -37385,10 +37385,10 @@
         <v>0</v>
       </c>
       <c r="X262" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y262" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z262" t="n">
         <v>0</v>
@@ -37454,22 +37454,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -37490,13 +37490,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M263" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N263" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -37520,16 +37520,16 @@
         <v>0</v>
       </c>
       <c r="V263" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W263" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="X263" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Y263" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z263" t="n">
         <v>0</v>
@@ -37736,22 +37736,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -37772,13 +37772,13 @@
         </is>
       </c>
       <c r="L265" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M265" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N265" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O265" t="n">
         <v>0</v>
@@ -37808,10 +37808,10 @@
         <v>0</v>
       </c>
       <c r="X265" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y265" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z265" t="n">
         <v>0</v>
@@ -37877,22 +37877,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -37913,13 +37913,13 @@
         </is>
       </c>
       <c r="L266" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M266" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N266" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O266" t="n">
         <v>0</v>
@@ -37943,16 +37943,16 @@
         <v>0</v>
       </c>
       <c r="V266" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W266" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="X266" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y266" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z266" t="n">
         <v>0</v>
@@ -38159,22 +38159,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -38300,22 +38300,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -38723,22 +38723,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -39861,12 +39861,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -39992,7 +39992,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -40002,12 +40002,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -40133,7 +40133,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -40143,12 +40143,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -40169,13 +40169,13 @@
         </is>
       </c>
       <c r="L282" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M282" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N282" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O282" t="n">
         <v>0</v>
@@ -40211,10 +40211,10 @@
         <v>0</v>
       </c>
       <c r="Z282" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA282" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB282" t="n">
         <v>0</v>
@@ -40274,7 +40274,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -40284,12 +40284,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -40310,13 +40310,13 @@
         </is>
       </c>
       <c r="L283" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M283" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N283" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O283" t="n">
         <v>0</v>
@@ -40352,10 +40352,10 @@
         <v>0</v>
       </c>
       <c r="Z283" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA283" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB283" t="n">
         <v>0</v>
@@ -40415,7 +40415,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -40425,12 +40425,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -40556,7 +40556,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -40566,12 +40566,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Wilstermann</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -40592,13 +40592,13 @@
         </is>
       </c>
       <c r="L285" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M285" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N285" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O285" t="n">
         <v>0</v>
@@ -40628,10 +40628,10 @@
         <v>0</v>
       </c>
       <c r="X285" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y285" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z285" t="n">
         <v>0</v>
@@ -40697,7 +40697,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -40707,12 +40707,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Wilstermann</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -40733,13 +40733,13 @@
         </is>
       </c>
       <c r="L286" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M286" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N286" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O286" t="n">
         <v>0</v>
@@ -40769,10 +40769,10 @@
         <v>0</v>
       </c>
       <c r="X286" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y286" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z286" t="n">
         <v>0</v>

--- a/jogos_2025-08-24.xlsx
+++ b/jogos_2025-08-24.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ming Chuan University</t>
+          <t>Tatung</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hang Yuen FC</t>
+          <t>Tainan City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tatung</t>
+          <t>Ming Chuan University</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tainan City</t>
+          <t>Hang Yuen FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,22 +2627,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2768,22 +2768,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3191,22 +3191,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3332,22 +3332,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3692,10 +3692,10 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3827,10 +3827,10 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.28</v>
+        <v>2.9</v>
       </c>
       <c r="M25" t="n">
-        <v>5.4</v>
+        <v>3.65</v>
       </c>
       <c r="N25" t="n">
-        <v>9.199999999999999</v>
+        <v>2.16</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3968,16 +3968,16 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -4037,22 +4037,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Taiwan Taiwan Football Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Taichung Rock</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Taichung Futuro</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4178,22 +4178,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4319,22 +4319,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4460,22 +4460,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Taiwan Taiwan Football Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Taipower</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>AC Taipei</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4742,22 +4742,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4820,10 +4820,10 @@
         <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
@@ -4883,22 +4883,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Taiwan Taiwan Football Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Taichung Rock</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Taichung Futuro</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5024,22 +5024,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5060,13 +5060,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5102,10 +5102,10 @@
         <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5306,22 +5306,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Taiwan Taiwan Football Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Taipower</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AC Taipei</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5588,22 +5588,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5660,10 +5660,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
         <v>0</v>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5801,16 +5801,16 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB38" t="n">
         <v>0</v>
@@ -5870,22 +5870,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6188,13 +6188,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -6224,10 +6224,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
@@ -6585,12 +6585,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6611,13 +6611,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.6</v>
+        <v>1.85</v>
       </c>
       <c r="M44" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="N44" t="n">
-        <v>2.55</v>
+        <v>4.1</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6647,16 +6647,16 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
         <v>0</v>
@@ -6998,22 +6998,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7139,22 +7139,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7562,22 +7562,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7703,22 +7703,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7844,22 +7844,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7985,22 +7985,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8136,12 +8136,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9149,13 +9149,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
         <v>0</v>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -9290,13 +9290,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -9326,10 +9326,10 @@
         <v>0</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Z63" t="n">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9431,10 +9431,10 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="M64" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="N64" t="n">
         <v>5.2</v>
@@ -9467,16 +9467,16 @@
         <v>0</v>
       </c>
       <c r="X64" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB64" t="n">
         <v>0</v>
@@ -9677,22 +9677,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10100,22 +10100,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -10277,13 +10277,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -10313,10 +10313,10 @@
         <v>0</v>
       </c>
       <c r="X70" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -10418,13 +10418,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -10454,10 +10454,10 @@
         <v>0</v>
       </c>
       <c r="X71" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z71" t="n">
         <v>0</v>
@@ -10523,7 +10523,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10559,13 +10559,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -10595,10 +10595,10 @@
         <v>0</v>
       </c>
       <c r="X72" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
         <v>0</v>
@@ -10664,22 +10664,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10805,22 +10805,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10877,10 +10877,10 @@
         <v>0</v>
       </c>
       <c r="X74" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z74" t="n">
         <v>0</v>
@@ -10982,13 +10982,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="M75" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="N75" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -11012,10 +11012,10 @@
         <v>0</v>
       </c>
       <c r="V75" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W75" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="X75" t="n">
         <v>0</v>
@@ -11228,7 +11228,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -11238,12 +11238,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -11369,7 +11369,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>UNA Strassen</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -11405,13 +11405,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -11520,12 +11520,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -11802,12 +11802,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11933,7 +11933,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11943,12 +11943,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11965,7 +11965,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L82" t="n">
@@ -12084,12 +12084,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>UN Käerjéng</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -12215,7 +12215,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -12356,22 +12356,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -12497,22 +12497,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -12648,12 +12648,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>UN Käerjéng</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12779,22 +12779,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Slutsk</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Neman Grodno</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12920,7 +12920,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12930,12 +12930,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -13061,7 +13061,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -13071,12 +13071,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -13202,7 +13202,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -13212,12 +13212,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>UNA Strassen</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -13234,7 +13234,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L91" t="n">
@@ -13343,7 +13343,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -13353,12 +13353,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Slutsk</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Neman Grodno</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -13484,22 +13484,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -13520,13 +13520,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -13625,22 +13625,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -13766,7 +13766,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13802,13 +13802,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -13838,10 +13838,10 @@
         <v>0</v>
       </c>
       <c r="X95" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z95" t="n">
         <v>0</v>
@@ -13907,22 +13907,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -14048,22 +14048,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -14261,10 +14261,10 @@
         <v>0</v>
       </c>
       <c r="X98" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z98" t="n">
         <v>0</v>
@@ -14340,12 +14340,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -14481,12 +14481,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -14612,22 +14612,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -14763,12 +14763,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -15176,22 +15176,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Komárno</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Spartak Trnava</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -15317,7 +15317,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -15349,7 +15349,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L106" t="n">
@@ -15599,22 +15599,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -15740,7 +15740,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -15750,12 +15750,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -15881,7 +15881,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -15891,12 +15891,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15917,13 +15917,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -15953,10 +15953,10 @@
         <v>0</v>
       </c>
       <c r="X110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y110" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z110" t="n">
         <v>0</v>
@@ -16022,7 +16022,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -16032,12 +16032,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -16173,12 +16173,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -16304,7 +16304,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -16314,12 +16314,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -16340,13 +16340,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -16376,10 +16376,10 @@
         <v>0</v>
       </c>
       <c r="X113" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Y113" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z113" t="n">
         <v>0</v>
@@ -16445,7 +16445,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -16455,12 +16455,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -16481,13 +16481,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -16517,10 +16517,10 @@
         <v>0</v>
       </c>
       <c r="X114" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Y114" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z114" t="n">
         <v>0</v>
@@ -16596,12 +16596,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -16727,7 +16727,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -16737,12 +16737,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -16759,7 +16759,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L116" t="n">
@@ -16868,7 +16868,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -16878,12 +16878,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -17150,7 +17150,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -17160,12 +17160,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -17291,22 +17291,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -17323,7 +17323,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L120" t="n">
@@ -17432,7 +17432,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -17442,12 +17442,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -17468,13 +17468,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -17504,10 +17504,10 @@
         <v>0</v>
       </c>
       <c r="X121" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z121" t="n">
         <v>0</v>
@@ -17573,7 +17573,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -17583,12 +17583,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -17609,13 +17609,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -17645,10 +17645,10 @@
         <v>0</v>
       </c>
       <c r="X122" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z122" t="n">
         <v>0</v>
@@ -17714,7 +17714,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -17724,12 +17724,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -17786,10 +17786,10 @@
         <v>0</v>
       </c>
       <c r="X123" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z123" t="n">
         <v>0</v>
@@ -17855,7 +17855,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -17996,22 +17996,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -18028,7 +18028,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L125" t="n">
@@ -18137,22 +18137,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -18169,7 +18169,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L126" t="n">
@@ -18278,7 +18278,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -18288,12 +18288,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -18310,7 +18310,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L127" t="n">
@@ -18419,7 +18419,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -18429,12 +18429,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -18560,7 +18560,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -18570,12 +18570,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L129" t="n">
@@ -18701,7 +18701,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -18711,12 +18711,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -18842,7 +18842,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -18852,12 +18852,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -18983,7 +18983,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -18993,12 +18993,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -19265,7 +19265,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -19416,12 +19416,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -19547,7 +19547,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -19557,12 +19557,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -19698,12 +19698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -19839,12 +19839,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Ironi Ramat HaSharon</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -19970,22 +19970,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -20121,12 +20121,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -20262,12 +20262,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -20393,7 +20393,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -20403,12 +20403,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -20534,7 +20534,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -20544,12 +20544,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -20566,7 +20566,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L143" t="n">
@@ -20675,7 +20675,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -20685,12 +20685,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -20711,13 +20711,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M144" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N144" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -20747,10 +20747,10 @@
         <v>0</v>
       </c>
       <c r="X144" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y144" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z144" t="n">
         <v>0</v>
@@ -20816,7 +20816,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -20826,12 +20826,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -20957,7 +20957,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -20967,12 +20967,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -21098,7 +21098,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -21108,12 +21108,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Ironi Ramat HaSharon</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -21134,13 +21134,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M147" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N147" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -21170,10 +21170,10 @@
         <v>0</v>
       </c>
       <c r="X147" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y147" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z147" t="n">
         <v>0</v>
@@ -21239,7 +21239,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -21249,12 +21249,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -21275,13 +21275,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M148" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N148" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -21311,10 +21311,10 @@
         <v>0</v>
       </c>
       <c r="X148" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Y148" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z148" t="n">
         <v>0</v>
@@ -21380,7 +21380,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -21390,12 +21390,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -21416,13 +21416,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M149" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N149" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -21452,10 +21452,10 @@
         <v>0</v>
       </c>
       <c r="X149" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Y149" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z149" t="n">
         <v>0</v>
@@ -21521,7 +21521,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -21531,12 +21531,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -21662,7 +21662,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -21672,12 +21672,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -21813,12 +21813,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -21944,7 +21944,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -21954,12 +21954,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -22085,7 +22085,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -22095,12 +22095,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -22367,7 +22367,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -22377,12 +22377,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -22508,7 +22508,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -22518,12 +22518,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Komárno</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Spartak Trnava</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -22649,7 +22649,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -22659,12 +22659,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -23495,7 +23495,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -23505,12 +23505,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -23531,13 +23531,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M164" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N164" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -23567,10 +23567,10 @@
         <v>0</v>
       </c>
       <c r="X164" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y164" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z164" t="n">
         <v>0</v>
@@ -23636,7 +23636,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -23646,12 +23646,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -23672,13 +23672,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M165" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N165" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -23708,10 +23708,10 @@
         <v>0</v>
       </c>
       <c r="X165" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Y165" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z165" t="n">
         <v>0</v>
@@ -23777,7 +23777,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -23787,12 +23787,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -23813,13 +23813,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M166" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N166" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -23849,16 +23849,16 @@
         <v>0</v>
       </c>
       <c r="X166" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Y166" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z166" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA166" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB166" t="n">
         <v>0</v>
@@ -24059,7 +24059,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -24069,12 +24069,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -24200,7 +24200,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -24210,12 +24210,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -24341,7 +24341,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -24351,12 +24351,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -24377,13 +24377,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M170" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N170" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -24413,16 +24413,16 @@
         <v>0</v>
       </c>
       <c r="X170" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Y170" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z170" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA170" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB170" t="n">
         <v>0</v>
@@ -24482,7 +24482,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -24492,12 +24492,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -24623,7 +24623,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -24633,12 +24633,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -24915,12 +24915,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -25046,7 +25046,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -25056,12 +25056,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -25187,22 +25187,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -25328,22 +25328,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -25469,7 +25469,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -25479,12 +25479,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -25610,7 +25610,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -25620,12 +25620,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -25751,7 +25751,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -25761,12 +25761,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -25902,12 +25902,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -26033,22 +26033,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -26174,22 +26174,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -26315,7 +26315,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -26325,12 +26325,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -26456,7 +26456,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -26466,12 +26466,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -26597,22 +26597,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -26738,7 +26738,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -26748,12 +26748,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -26889,12 +26889,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -27030,12 +27030,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -27161,22 +27161,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -27302,7 +27302,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -27312,12 +27312,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -27443,7 +27443,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -27453,12 +27453,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -27584,7 +27584,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -27594,12 +27594,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -27725,7 +27725,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -27735,12 +27735,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -27866,7 +27866,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -27876,12 +27876,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -28007,7 +28007,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -28017,12 +28017,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -28148,7 +28148,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -28158,12 +28158,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -28289,7 +28289,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -28299,12 +28299,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -28430,7 +28430,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -28440,12 +28440,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -28581,12 +28581,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -28712,7 +28712,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -28722,12 +28722,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -28853,7 +28853,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -28863,12 +28863,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -29004,12 +29004,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -29135,7 +29135,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -29145,12 +29145,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -29276,7 +29276,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -29286,12 +29286,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -29427,12 +29427,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -29558,7 +29558,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -29568,12 +29568,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -29594,13 +29594,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M207" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N207" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -29630,10 +29630,10 @@
         <v>0</v>
       </c>
       <c r="X207" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y207" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z207" t="n">
         <v>0</v>
@@ -29699,7 +29699,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -29709,12 +29709,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -29840,22 +29840,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -29876,13 +29876,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M209" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N209" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -29912,10 +29912,10 @@
         <v>0</v>
       </c>
       <c r="X209" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Y209" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z209" t="n">
         <v>0</v>
@@ -29981,22 +29981,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -30132,12 +30132,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -30158,13 +30158,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>3.15</v>
+        <v>2.55</v>
       </c>
       <c r="M211" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N211" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -30194,10 +30194,10 @@
         <v>0</v>
       </c>
       <c r="X211" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="Y211" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="Z211" t="n">
         <v>0</v>
@@ -30263,7 +30263,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -30273,12 +30273,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -30545,22 +30545,22 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -30686,7 +30686,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -30696,12 +30696,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Podbrezová</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -30968,22 +30968,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -31109,7 +31109,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -31119,12 +31119,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -31250,7 +31250,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -31260,12 +31260,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -31391,22 +31391,22 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Kolkheti Poti</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -31532,7 +31532,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -31542,12 +31542,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Kolkheti Poti</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -31673,7 +31673,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -31683,12 +31683,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Podbrezová</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -31814,7 +31814,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -31824,12 +31824,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -31955,22 +31955,22 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -32106,12 +32106,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -32519,22 +32519,22 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -32660,7 +32660,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -32670,12 +32670,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -32801,22 +32801,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -32837,13 +32837,13 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="M230" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N230" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O230" t="n">
         <v>0</v>
@@ -32879,10 +32879,10 @@
         <v>0</v>
       </c>
       <c r="Z230" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA230" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB230" t="n">
         <v>0</v>
@@ -32942,7 +32942,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -32952,12 +32952,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -33224,7 +33224,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -33234,12 +33234,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -33647,22 +33647,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>CD El Nacional</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -33788,7 +33788,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -33798,12 +33798,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -33824,13 +33824,13 @@
         </is>
       </c>
       <c r="L237" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="M237" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="N237" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="O237" t="n">
         <v>0</v>
@@ -33860,10 +33860,10 @@
         <v>0</v>
       </c>
       <c r="X237" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Y237" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Z237" t="n">
         <v>0</v>
@@ -33929,7 +33929,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -33939,12 +33939,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -33965,13 +33965,13 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="M238" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="N238" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="O238" t="n">
         <v>0</v>
@@ -34001,10 +34001,10 @@
         <v>0</v>
       </c>
       <c r="X238" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Y238" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Z238" t="n">
         <v>0</v>
@@ -34070,22 +34070,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -34211,22 +34211,22 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>CD El Nacional</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -34352,22 +34352,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -34775,22 +34775,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -34916,22 +34916,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -35057,22 +35057,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -35198,7 +35198,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -35208,12 +35208,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -35234,13 +35234,13 @@
         </is>
       </c>
       <c r="L247" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M247" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N247" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O247" t="n">
         <v>0</v>
@@ -35270,10 +35270,10 @@
         <v>0</v>
       </c>
       <c r="X247" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Y247" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z247" t="n">
         <v>0</v>
@@ -35339,22 +35339,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -35490,12 +35490,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -35621,22 +35621,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -35657,13 +35657,13 @@
         </is>
       </c>
       <c r="L250" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M250" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N250" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="O250" t="n">
         <v>0</v>
@@ -35693,10 +35693,10 @@
         <v>0</v>
       </c>
       <c r="X250" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y250" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z250" t="n">
         <v>0</v>
@@ -35762,22 +35762,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -35913,12 +35913,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -36054,12 +36054,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -36185,7 +36185,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -36195,12 +36195,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -36221,13 +36221,13 @@
         </is>
       </c>
       <c r="L254" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M254" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N254" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="O254" t="n">
         <v>0</v>
@@ -36257,10 +36257,10 @@
         <v>0</v>
       </c>
       <c r="X254" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Y254" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z254" t="n">
         <v>0</v>
@@ -36467,7 +36467,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -36477,12 +36477,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -36503,13 +36503,13 @@
         </is>
       </c>
       <c r="L256" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M256" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N256" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="O256" t="n">
         <v>0</v>
@@ -36539,10 +36539,10 @@
         <v>0</v>
       </c>
       <c r="X256" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Y256" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z256" t="n">
         <v>0</v>
@@ -36890,22 +36890,22 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -37031,22 +37031,22 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -37172,22 +37172,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -37313,7 +37313,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -37323,12 +37323,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -37454,22 +37454,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -37595,7 +37595,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -37605,12 +37605,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -37736,7 +37736,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -37746,12 +37746,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -37772,13 +37772,13 @@
         </is>
       </c>
       <c r="L265" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M265" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N265" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O265" t="n">
         <v>0</v>
@@ -37808,10 +37808,10 @@
         <v>0</v>
       </c>
       <c r="X265" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y265" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z265" t="n">
         <v>0</v>
@@ -37887,12 +37887,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -37913,13 +37913,13 @@
         </is>
       </c>
       <c r="L266" t="n">
-        <v>2.46</v>
+        <v>1.73</v>
       </c>
       <c r="M266" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="N266" t="n">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="O266" t="n">
         <v>0</v>
@@ -37943,16 +37943,16 @@
         <v>0</v>
       </c>
       <c r="V266" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W266" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="X266" t="n">
-        <v>2.53</v>
+        <v>2.25</v>
       </c>
       <c r="Y266" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="Z266" t="n">
         <v>0</v>
@@ -38018,22 +38018,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -38054,13 +38054,13 @@
         </is>
       </c>
       <c r="L267" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M267" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N267" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O267" t="n">
         <v>0</v>
@@ -38084,16 +38084,16 @@
         <v>0</v>
       </c>
       <c r="V267" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W267" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="X267" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y267" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z267" t="n">
         <v>0</v>
@@ -38159,22 +38159,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -38300,7 +38300,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -38310,12 +38310,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -38441,22 +38441,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -38582,22 +38582,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -38864,7 +38864,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -38874,12 +38874,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -38900,13 +38900,13 @@
         </is>
       </c>
       <c r="L273" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M273" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N273" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O273" t="n">
         <v>0</v>
@@ -38936,10 +38936,10 @@
         <v>0</v>
       </c>
       <c r="X273" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Y273" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z273" t="n">
         <v>0</v>
@@ -39005,7 +39005,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -39015,12 +39015,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -39041,13 +39041,13 @@
         </is>
       </c>
       <c r="L274" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M274" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N274" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O274" t="n">
         <v>0</v>
@@ -39077,10 +39077,10 @@
         <v>0</v>
       </c>
       <c r="X274" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Y274" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z274" t="n">
         <v>0</v>
@@ -39428,7 +39428,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -39438,12 +39438,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -39464,13 +39464,13 @@
         </is>
       </c>
       <c r="L277" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M277" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N277" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O277" t="n">
         <v>0</v>
@@ -39500,10 +39500,10 @@
         <v>0</v>
       </c>
       <c r="X277" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Y277" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Z277" t="n">
         <v>0</v>
@@ -39579,12 +39579,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -39605,14 +39605,14 @@
         </is>
       </c>
       <c r="L278" t="n">
-        <v>4.7</v>
+        <v>2.08</v>
       </c>
       <c r="M278" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N278" t="n">
         <v>3.55</v>
       </c>
-      <c r="N278" t="n">
-        <v>1.71</v>
-      </c>
       <c r="O278" t="n">
         <v>0</v>
       </c>
@@ -39641,10 +39641,10 @@
         <v>0</v>
       </c>
       <c r="X278" t="n">
-        <v>2.37</v>
+        <v>2.44</v>
       </c>
       <c r="Y278" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="Z278" t="n">
         <v>0</v>
@@ -39710,7 +39710,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -39720,12 +39720,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -39746,13 +39746,13 @@
         </is>
       </c>
       <c r="L279" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="M279" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N279" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O279" t="n">
         <v>0</v>
@@ -39782,10 +39782,10 @@
         <v>0</v>
       </c>
       <c r="X279" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Y279" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z279" t="n">
         <v>0</v>
@@ -39851,7 +39851,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -39861,12 +39861,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -39887,13 +39887,13 @@
         </is>
       </c>
       <c r="L280" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M280" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N280" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O280" t="n">
         <v>0</v>
@@ -39929,10 +39929,10 @@
         <v>0</v>
       </c>
       <c r="Z280" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA280" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB280" t="n">
         <v>0</v>
@@ -39992,7 +39992,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -40002,12 +40002,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -40133,7 +40133,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -40143,12 +40143,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -40274,7 +40274,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -40284,12 +40284,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -40310,13 +40310,13 @@
         </is>
       </c>
       <c r="L283" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M283" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N283" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O283" t="n">
         <v>0</v>
@@ -40352,10 +40352,10 @@
         <v>0</v>
       </c>
       <c r="Z283" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA283" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB283" t="n">
         <v>0</v>
@@ -40415,7 +40415,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -40425,12 +40425,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G284" t="n">

--- a/jogos_2025-08-24.xlsx
+++ b/jogos_2025-08-24.xlsx
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,22 +2627,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2768,22 +2768,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3191,22 +3191,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3332,22 +3332,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3692,10 +3692,10 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3974,10 +3974,10 @@
         <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4742,22 +4742,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4820,10 +4820,10 @@
         <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5342,13 +5342,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5384,10 +5384,10 @@
         <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
@@ -5447,22 +5447,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5588,22 +5588,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5729,22 +5729,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5801,16 +5801,16 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
         <v>0</v>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5906,13 +5906,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5942,16 +5942,16 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
@@ -6152,7 +6152,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6188,13 +6188,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -6224,10 +6224,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6329,13 +6329,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6365,10 +6365,10 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -6434,22 +6434,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6611,13 +6611,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
         <v>0</v>
@@ -6857,22 +6857,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6998,22 +6998,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7139,7 +7139,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7280,22 +7280,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Isloch</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitebsk</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7562,22 +7562,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7703,22 +7703,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7985,22 +7985,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -8136,12 +8136,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8267,22 +8267,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8408,22 +8408,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Isloch</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Vitebsk</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8559,12 +8559,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8972,22 +8972,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9008,13 +9008,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -9044,10 +9044,10 @@
         <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Z61" t="n">
         <v>0</v>
@@ -9113,7 +9113,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9149,13 +9149,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB62" t="n">
         <v>0</v>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -9290,13 +9290,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -9326,10 +9326,10 @@
         <v>0</v>
       </c>
       <c r="X63" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
         <v>0</v>
@@ -9395,22 +9395,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9431,13 +9431,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -9473,10 +9473,10 @@
         <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
         <v>0</v>
@@ -9677,22 +9677,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9818,22 +9818,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9959,22 +9959,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -10100,22 +10100,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -10241,22 +10241,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -10418,13 +10418,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.75</v>
+        <v>2.24</v>
       </c>
       <c r="M71" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N71" t="n">
-        <v>2.55</v>
+        <v>3.35</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -10454,10 +10454,10 @@
         <v>0</v>
       </c>
       <c r="X71" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="Z71" t="n">
         <v>0</v>
@@ -10523,22 +10523,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10674,12 +10674,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10700,13 +10700,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10736,10 +10736,10 @@
         <v>0</v>
       </c>
       <c r="X73" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z73" t="n">
         <v>0</v>
@@ -10805,7 +10805,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10877,10 +10877,10 @@
         <v>0</v>
       </c>
       <c r="X74" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z74" t="n">
         <v>0</v>
@@ -11228,22 +11228,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -11369,7 +11369,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>UNA Strassen</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -11405,13 +11405,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -11520,12 +11520,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -11661,12 +11661,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11802,12 +11802,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11933,22 +11933,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Slutsk</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Neman Grodno</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11965,7 +11965,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L82" t="n">
@@ -12084,12 +12084,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>UN Käerjéng</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -12215,7 +12215,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -12356,7 +12356,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -12497,7 +12497,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>UN Käerjéng</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -12638,7 +12638,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -12648,12 +12648,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12674,13 +12674,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -12779,22 +12779,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Slutsk</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Neman Grodno</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12920,7 +12920,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12930,12 +12930,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12952,7 +12952,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L89" t="n">
@@ -13061,7 +13061,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -13071,12 +13071,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -13202,7 +13202,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -13212,12 +13212,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>UNA Strassen</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -13343,22 +13343,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -13484,7 +13484,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -13494,12 +13494,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -13625,22 +13625,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -13766,22 +13766,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13802,13 +13802,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -13838,10 +13838,10 @@
         <v>0</v>
       </c>
       <c r="X95" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z95" t="n">
         <v>0</v>
@@ -13917,12 +13917,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -14048,7 +14048,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -14340,12 +14340,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -14471,22 +14471,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -14612,22 +14612,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -14753,22 +14753,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -14789,13 +14789,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -14825,10 +14825,10 @@
         <v>0</v>
       </c>
       <c r="X102" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Y102" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z102" t="n">
         <v>0</v>
@@ -15176,7 +15176,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -15186,12 +15186,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Komárno</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Spartak Trnava</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -15317,22 +15317,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -15349,7 +15349,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L106" t="n">
@@ -15458,22 +15458,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -15599,22 +15599,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -15631,7 +15631,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L108" t="n">
@@ -15740,7 +15740,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -15750,12 +15750,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -15881,22 +15881,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15917,13 +15917,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -15953,10 +15953,10 @@
         <v>0</v>
       </c>
       <c r="X110" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z110" t="n">
         <v>0</v>
@@ -16022,7 +16022,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -16032,12 +16032,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -16173,12 +16173,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -16199,13 +16199,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -16235,10 +16235,10 @@
         <v>0</v>
       </c>
       <c r="X112" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y112" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z112" t="n">
         <v>0</v>
@@ -16304,7 +16304,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -16314,12 +16314,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -16340,13 +16340,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -16376,10 +16376,10 @@
         <v>0</v>
       </c>
       <c r="X113" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z113" t="n">
         <v>0</v>
@@ -16445,7 +16445,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -16455,12 +16455,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -16481,13 +16481,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -16517,10 +16517,10 @@
         <v>0</v>
       </c>
       <c r="X114" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z114" t="n">
         <v>0</v>
@@ -16586,7 +16586,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -16596,12 +16596,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -16618,7 +16618,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L115" t="n">
@@ -16727,7 +16727,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -16737,12 +16737,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -16759,7 +16759,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L116" t="n">
@@ -16868,7 +16868,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -16878,12 +16878,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -16900,7 +16900,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L117" t="n">
@@ -17009,7 +17009,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -17019,12 +17019,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -17150,22 +17150,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -17182,7 +17182,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L119" t="n">
@@ -17291,22 +17291,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -17323,7 +17323,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L120" t="n">
@@ -17432,7 +17432,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -17442,12 +17442,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -17573,7 +17573,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -17583,12 +17583,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -17714,7 +17714,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -17724,12 +17724,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -17746,7 +17746,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L123" t="n">
@@ -17855,7 +17855,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -17996,7 +17996,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -18006,12 +18006,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -18137,22 +18137,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -18169,7 +18169,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L126" t="n">
@@ -18278,7 +18278,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -18288,12 +18288,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -18419,7 +18419,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -18429,12 +18429,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Ironi Ramat HaSharon</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -18560,22 +18560,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L129" t="n">
@@ -18701,7 +18701,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -18711,12 +18711,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -18842,7 +18842,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -18852,12 +18852,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -18983,7 +18983,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -18993,12 +18993,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -19160,13 +19160,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -19196,10 +19196,10 @@
         <v>0</v>
       </c>
       <c r="X133" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Y133" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z133" t="n">
         <v>0</v>
@@ -19265,7 +19265,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -19406,7 +19406,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -19416,12 +19416,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -19547,7 +19547,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -19557,12 +19557,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -19688,7 +19688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -19698,12 +19698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -19839,12 +19839,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ironi Ramat HaSharon</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -19980,12 +19980,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -20006,13 +20006,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -20042,10 +20042,10 @@
         <v>0</v>
       </c>
       <c r="X139" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y139" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z139" t="n">
         <v>0</v>
@@ -20111,7 +20111,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -20121,12 +20121,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -20393,7 +20393,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -20403,12 +20403,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -20534,7 +20534,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -20544,12 +20544,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Komárno</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Spartak Trnava</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -20675,7 +20675,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -20685,12 +20685,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -20816,7 +20816,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -20826,12 +20826,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -20957,7 +20957,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -20967,12 +20967,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -21098,7 +21098,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -21108,12 +21108,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -21134,13 +21134,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N147" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -21170,10 +21170,10 @@
         <v>0</v>
       </c>
       <c r="X147" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y147" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z147" t="n">
         <v>0</v>
@@ -21239,7 +21239,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -21249,12 +21249,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -21380,7 +21380,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -21390,12 +21390,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -21416,13 +21416,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M149" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N149" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -21452,10 +21452,10 @@
         <v>0</v>
       </c>
       <c r="X149" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Y149" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z149" t="n">
         <v>0</v>
@@ -21521,7 +21521,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -21531,12 +21531,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -21662,7 +21662,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -21672,12 +21672,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -21698,13 +21698,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M151" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -21734,10 +21734,10 @@
         <v>0</v>
       </c>
       <c r="X151" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y151" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z151" t="n">
         <v>0</v>
@@ -21803,7 +21803,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -21813,12 +21813,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -21944,7 +21944,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -21954,12 +21954,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -22085,7 +22085,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -22095,12 +22095,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -22367,7 +22367,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -22377,12 +22377,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -22518,12 +22518,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -22649,7 +22649,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -22659,12 +22659,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -22685,13 +22685,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M158" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -22721,10 +22721,10 @@
         <v>0</v>
       </c>
       <c r="X158" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Y158" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z158" t="n">
         <v>0</v>
@@ -23354,7 +23354,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -23364,12 +23364,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -23390,13 +23390,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M163" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N163" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -23426,10 +23426,10 @@
         <v>0</v>
       </c>
       <c r="X163" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Y163" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z163" t="n">
         <v>0</v>
@@ -23495,7 +23495,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -23505,12 +23505,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -23531,13 +23531,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="M164" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="N164" t="n">
-        <v>5.8</v>
+        <v>3.45</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -23567,16 +23567,16 @@
         <v>0</v>
       </c>
       <c r="X164" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="Y164" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="Z164" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA164" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB164" t="n">
         <v>0</v>
@@ -23636,7 +23636,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -23646,12 +23646,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -23777,7 +23777,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -23787,12 +23787,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -23813,13 +23813,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N166" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -23849,16 +23849,16 @@
         <v>0</v>
       </c>
       <c r="X166" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Y166" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z166" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA166" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB166" t="n">
         <v>0</v>
@@ -23918,7 +23918,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -23928,12 +23928,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -24059,7 +24059,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -24069,12 +24069,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -24200,7 +24200,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -24210,12 +24210,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -24482,7 +24482,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -24492,12 +24492,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -24518,13 +24518,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M171" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N171" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -24554,10 +24554,10 @@
         <v>0</v>
       </c>
       <c r="X171" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y171" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z171" t="n">
         <v>0</v>
@@ -24623,7 +24623,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -24633,12 +24633,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -24659,13 +24659,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M172" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N172" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -24695,10 +24695,10 @@
         <v>0</v>
       </c>
       <c r="X172" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Y172" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z172" t="n">
         <v>0</v>
@@ -25046,7 +25046,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -25056,12 +25056,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -25328,22 +25328,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -25469,22 +25469,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -25610,7 +25610,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -25620,12 +25620,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -25761,12 +25761,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -25892,22 +25892,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -26033,22 +26033,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -26174,7 +26174,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -26184,12 +26184,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -26315,22 +26315,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -26456,7 +26456,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -26466,12 +26466,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -26607,12 +26607,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -26738,22 +26738,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -27020,7 +27020,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -27030,12 +27030,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -27161,7 +27161,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -27171,12 +27171,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -27302,22 +27302,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -27443,7 +27443,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -27453,12 +27453,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -27725,7 +27725,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -27735,12 +27735,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -27866,7 +27866,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -27876,12 +27876,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -28158,12 +28158,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -28289,7 +28289,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -28299,12 +28299,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -28440,12 +28440,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -28581,12 +28581,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -28712,7 +28712,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -28722,12 +28722,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -28863,12 +28863,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -29004,12 +29004,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -29276,22 +29276,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -29568,12 +29568,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -29594,13 +29594,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>3.15</v>
+        <v>2.55</v>
       </c>
       <c r="M207" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N207" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -29630,10 +29630,10 @@
         <v>0</v>
       </c>
       <c r="X207" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="Y207" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="Z207" t="n">
         <v>0</v>
@@ -29699,7 +29699,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -29709,12 +29709,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -29840,22 +29840,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -29981,22 +29981,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -30132,12 +30132,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -30158,13 +30158,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>2.55</v>
+        <v>3.15</v>
       </c>
       <c r="M211" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N211" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -30194,10 +30194,10 @@
         <v>0</v>
       </c>
       <c r="X211" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="Y211" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="Z211" t="n">
         <v>0</v>
@@ -30263,7 +30263,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -30273,12 +30273,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -30686,7 +30686,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -30696,12 +30696,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -30827,22 +30827,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -30968,22 +30968,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Kolkheti Poti</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -31260,12 +31260,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -31391,22 +31391,22 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Kolkheti Poti</t>
+          <t>Podbrezová</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -31532,22 +31532,22 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -31673,7 +31673,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -31683,12 +31683,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Podbrezová</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -31814,7 +31814,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -31824,12 +31824,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -31955,7 +31955,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -31965,12 +31965,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -32096,7 +32096,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -32106,12 +32106,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -32237,7 +32237,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -32247,12 +32247,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -32378,7 +32378,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -32414,13 +32414,13 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>1.21</v>
+        <v>7.5</v>
       </c>
       <c r="M227" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="N227" t="n">
-        <v>11</v>
+        <v>1.28</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -32450,16 +32450,16 @@
         <v>0</v>
       </c>
       <c r="X227" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Y227" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Z227" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA227" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB227" t="n">
         <v>0</v>
@@ -32519,22 +32519,22 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -32660,7 +32660,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -32670,12 +32670,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -32696,13 +32696,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M229" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N229" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -32732,10 +32732,10 @@
         <v>0</v>
       </c>
       <c r="X229" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Y229" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Z229" t="n">
         <v>0</v>
@@ -32801,22 +32801,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -32837,13 +32837,13 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="M230" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N230" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="O230" t="n">
         <v>0</v>
@@ -32879,10 +32879,10 @@
         <v>0</v>
       </c>
       <c r="Z230" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA230" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB230" t="n">
         <v>0</v>
@@ -32942,7 +32942,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -32952,12 +32952,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -33083,7 +33083,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -33093,12 +33093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -33224,7 +33224,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -33234,12 +33234,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -33365,7 +33365,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -33375,12 +33375,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -33647,22 +33647,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>CD El Nacional</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -33929,7 +33929,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -33939,12 +33939,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -33965,13 +33965,13 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="M238" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="N238" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="O238" t="n">
         <v>0</v>
@@ -34001,10 +34001,10 @@
         <v>0</v>
       </c>
       <c r="X238" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Y238" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Z238" t="n">
         <v>0</v>
@@ -34070,22 +34070,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -34106,13 +34106,13 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="M239" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="N239" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="O239" t="n">
         <v>0</v>
@@ -34142,10 +34142,10 @@
         <v>0</v>
       </c>
       <c r="X239" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Y239" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Z239" t="n">
         <v>0</v>
@@ -34211,22 +34211,22 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>CD El Nacional</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -34352,22 +34352,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -34916,22 +34916,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -35057,22 +35057,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -35198,7 +35198,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -35208,12 +35208,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -35349,12 +35349,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -35480,22 +35480,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -35772,12 +35772,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -35913,12 +35913,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -36044,22 +36044,22 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -36185,7 +36185,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -36195,12 +36195,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -36221,13 +36221,13 @@
         </is>
       </c>
       <c r="L254" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M254" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N254" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="O254" t="n">
         <v>0</v>
@@ -36257,10 +36257,10 @@
         <v>0</v>
       </c>
       <c r="X254" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Y254" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z254" t="n">
         <v>0</v>
@@ -36336,12 +36336,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -36362,13 +36362,13 @@
         </is>
       </c>
       <c r="L255" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="M255" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="N255" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="O255" t="n">
         <v>0</v>
@@ -36398,10 +36398,10 @@
         <v>0</v>
       </c>
       <c r="X255" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="Y255" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Z255" t="n">
         <v>0</v>
@@ -36467,7 +36467,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -36477,12 +36477,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -36503,13 +36503,13 @@
         </is>
       </c>
       <c r="L256" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M256" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N256" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="O256" t="n">
         <v>0</v>
@@ -36539,10 +36539,10 @@
         <v>0</v>
       </c>
       <c r="X256" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Y256" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z256" t="n">
         <v>0</v>
@@ -36608,22 +36608,22 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -36749,22 +36749,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -36890,22 +36890,22 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -37031,7 +37031,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -37041,12 +37041,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -37172,22 +37172,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -37323,12 +37323,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -37454,22 +37454,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -37595,22 +37595,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -37631,13 +37631,13 @@
         </is>
       </c>
       <c r="L264" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M264" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N264" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O264" t="n">
         <v>0</v>
@@ -37667,10 +37667,10 @@
         <v>0</v>
       </c>
       <c r="X264" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y264" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z264" t="n">
         <v>0</v>
@@ -37736,22 +37736,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -37877,22 +37877,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -37913,13 +37913,13 @@
         </is>
       </c>
       <c r="L266" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M266" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N266" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O266" t="n">
         <v>0</v>
@@ -37949,10 +37949,10 @@
         <v>0</v>
       </c>
       <c r="X266" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y266" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z266" t="n">
         <v>0</v>
@@ -38159,7 +38159,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -38169,12 +38169,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -38300,22 +38300,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -38441,22 +38441,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -38582,22 +38582,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -38723,22 +38723,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -38864,7 +38864,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -38874,12 +38874,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -38900,13 +38900,13 @@
         </is>
       </c>
       <c r="L273" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M273" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N273" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O273" t="n">
         <v>0</v>
@@ -38936,10 +38936,10 @@
         <v>0</v>
       </c>
       <c r="X273" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Y273" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z273" t="n">
         <v>0</v>
@@ -39005,7 +39005,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -39015,12 +39015,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -39041,13 +39041,13 @@
         </is>
       </c>
       <c r="L274" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M274" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N274" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O274" t="n">
         <v>0</v>
@@ -39077,10 +39077,10 @@
         <v>0</v>
       </c>
       <c r="X274" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Y274" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z274" t="n">
         <v>0</v>
@@ -39851,7 +39851,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -39861,12 +39861,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -39887,13 +39887,13 @@
         </is>
       </c>
       <c r="L280" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M280" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N280" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O280" t="n">
         <v>0</v>
@@ -39929,10 +39929,10 @@
         <v>0</v>
       </c>
       <c r="Z280" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA280" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB280" t="n">
         <v>0</v>
@@ -40133,7 +40133,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -40143,12 +40143,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -40274,7 +40274,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -40284,12 +40284,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -40415,7 +40415,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -40425,12 +40425,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -40451,13 +40451,13 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M284" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N284" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O284" t="n">
         <v>0</v>
@@ -40493,10 +40493,10 @@
         <v>0</v>
       </c>
       <c r="Z284" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA284" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB284" t="n">
         <v>0</v>
@@ -40556,7 +40556,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -40566,12 +40566,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Wilstermann</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -40592,13 +40592,13 @@
         </is>
       </c>
       <c r="L285" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M285" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N285" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O285" t="n">
         <v>0</v>
@@ -40628,10 +40628,10 @@
         <v>0</v>
       </c>
       <c r="X285" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y285" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z285" t="n">
         <v>0</v>
@@ -40697,7 +40697,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -40707,12 +40707,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Wilstermann</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -40733,13 +40733,13 @@
         </is>
       </c>
       <c r="L286" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M286" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N286" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O286" t="n">
         <v>0</v>
@@ -40769,10 +40769,10 @@
         <v>0</v>
       </c>
       <c r="X286" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y286" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z286" t="n">
         <v>0</v>

--- a/jogos_2025-08-24.xlsx
+++ b/jogos_2025-08-24.xlsx
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tatung</t>
+          <t>Ming Chuan University</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tainan City</t>
+          <t>Hang Yuen FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ming Chuan University</t>
+          <t>Tatung</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hang Yuen FC</t>
+          <t>Tainan City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1958,13 +1958,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2276,10 +2276,10 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2558,10 +2558,10 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2699,10 +2699,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -2768,22 +2768,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,13 +2804,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2840,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3122,10 +3122,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,13 +3227,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3263,10 +3263,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -3332,22 +3332,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3545,10 +3545,10 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3692,10 +3692,10 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3974,10 +3974,10 @@
         <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4109,10 +4109,10 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Taiwan Taiwan Football Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Taichung Rock</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Taichung Futuro</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4319,22 +4319,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4397,10 +4397,10 @@
         <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -4460,22 +4460,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Taiwan Taiwan Football Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Taipower</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AC Taipei</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4742,22 +4742,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Taichung Rock</t>
+          <t>Taipower</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Taichung Futuro</t>
+          <t>AC Taipei</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5024,22 +5024,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5165,22 +5165,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5306,22 +5306,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5342,13 +5342,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5384,10 +5384,10 @@
         <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5660,10 +5660,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z37" t="n">
         <v>0</v>
@@ -5729,22 +5729,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6047,13 +6047,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -6083,10 +6083,10 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -6152,7 +6152,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6188,13 +6188,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -6224,10 +6224,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6329,13 +6329,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6365,10 +6365,10 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -6434,22 +6434,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6575,22 +6575,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6857,22 +6857,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7139,7 +7139,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7280,22 +7280,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7421,22 +7421,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Isloch</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Vitebsk</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7562,22 +7562,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7703,7 +7703,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7844,22 +7844,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7985,22 +7985,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -8136,12 +8136,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8267,22 +8267,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8408,22 +8408,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Isloch</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vitebsk</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8559,12 +8559,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9008,10 +9008,10 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="M61" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="N61" t="n">
         <v>5.2</v>
@@ -9044,16 +9044,16 @@
         <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB61" t="n">
         <v>0</v>
@@ -9123,12 +9123,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9149,10 +9149,10 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="M62" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="N62" t="n">
         <v>5.2</v>
@@ -9185,16 +9185,16 @@
         <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Z62" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
         <v>0</v>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9959,22 +9959,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -10241,22 +10241,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -10277,13 +10277,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -10313,10 +10313,10 @@
         <v>0</v>
       </c>
       <c r="X70" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z70" t="n">
         <v>0</v>
@@ -10382,22 +10382,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -10418,13 +10418,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -10454,10 +10454,10 @@
         <v>0</v>
       </c>
       <c r="X71" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
         <v>0</v>
@@ -10523,7 +10523,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10805,22 +10805,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -11228,22 +11228,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>UNA Strassen</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -11661,12 +11661,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11802,12 +11802,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>UN Käerjéng</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11933,22 +11933,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Slutsk</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Neman Grodno</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -12084,12 +12084,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>UNA Strassen</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -12356,22 +12356,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -12497,7 +12497,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>UN Käerjéng</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -12638,22 +12638,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Slutsk</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Neman Grodno</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12674,13 +12674,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -12779,7 +12779,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12789,12 +12789,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12815,13 +12815,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12920,7 +12920,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12930,12 +12930,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12952,7 +12952,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L89" t="n">
@@ -13061,7 +13061,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -13071,12 +13071,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -13093,7 +13093,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L90" t="n">
@@ -13202,7 +13202,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -13212,12 +13212,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -13343,7 +13343,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -13353,12 +13353,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -13625,22 +13625,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -13766,22 +13766,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13917,12 +13917,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -14048,7 +14048,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -14330,7 +14330,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -14340,12 +14340,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -14471,22 +14471,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -14612,22 +14612,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -14648,13 +14648,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -14684,10 +14684,10 @@
         <v>0</v>
       </c>
       <c r="X101" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z101" t="n">
         <v>0</v>
@@ -14753,22 +14753,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -14789,13 +14789,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -14825,10 +14825,10 @@
         <v>0</v>
       </c>
       <c r="X102" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
         <v>0</v>
@@ -15176,7 +15176,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -15186,12 +15186,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -15317,22 +15317,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -15458,7 +15458,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -15468,12 +15468,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Ironi Ramat HaSharon</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -15599,7 +15599,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -15609,12 +15609,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -15631,17 +15631,17 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -15671,10 +15671,10 @@
         <v>0</v>
       </c>
       <c r="X108" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z108" t="n">
         <v>0</v>
@@ -15740,7 +15740,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -15750,12 +15750,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -15881,22 +15881,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -16032,12 +16032,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -16173,12 +16173,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -16199,13 +16199,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -16235,10 +16235,10 @@
         <v>0</v>
       </c>
       <c r="X112" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z112" t="n">
         <v>0</v>
@@ -16314,12 +16314,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -16445,7 +16445,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -16455,12 +16455,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -16586,7 +16586,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -16596,12 +16596,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -16727,7 +16727,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -16737,12 +16737,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -16868,7 +16868,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -16878,12 +16878,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -17009,7 +17009,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -17019,12 +17019,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -17150,22 +17150,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -17182,7 +17182,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L119" t="n">
@@ -17301,12 +17301,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -17432,7 +17432,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -17442,12 +17442,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -17724,12 +17724,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -17855,7 +17855,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -18006,12 +18006,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -18137,7 +18137,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -18147,12 +18147,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -18278,7 +18278,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -18288,12 +18288,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -18419,7 +18419,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -18429,12 +18429,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ironi Ramat HaSharon</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -18560,22 +18560,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -18711,12 +18711,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -18842,22 +18842,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -18983,7 +18983,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -18993,12 +18993,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -19160,13 +19160,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -19196,10 +19196,10 @@
         <v>0</v>
       </c>
       <c r="X133" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Y133" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z133" t="n">
         <v>0</v>
@@ -19265,7 +19265,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -19301,13 +19301,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -19337,10 +19337,10 @@
         <v>0</v>
       </c>
       <c r="X134" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y134" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z134" t="n">
         <v>0</v>
@@ -19416,12 +19416,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -19547,7 +19547,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -19557,12 +19557,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -19688,7 +19688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -19698,12 +19698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -19724,13 +19724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M137" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -19760,10 +19760,10 @@
         <v>0</v>
       </c>
       <c r="X137" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Y137" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z137" t="n">
         <v>0</v>
@@ -19829,7 +19829,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -19839,12 +19839,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -19861,7 +19861,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L138" t="n">
@@ -19970,22 +19970,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -20006,13 +20006,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -20042,10 +20042,10 @@
         <v>0</v>
       </c>
       <c r="X139" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y139" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z139" t="n">
         <v>0</v>
@@ -20111,22 +20111,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -20143,7 +20143,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L140" t="n">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -20262,12 +20262,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -20393,7 +20393,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -20403,12 +20403,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -20534,7 +20534,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -20544,12 +20544,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Komárno</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Spartak Trnava</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -20675,7 +20675,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -20685,12 +20685,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -20816,7 +20816,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -20826,12 +20826,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -20852,13 +20852,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M145" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -20888,10 +20888,10 @@
         <v>0</v>
       </c>
       <c r="X145" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y145" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z145" t="n">
         <v>0</v>
@@ -20957,7 +20957,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -20967,12 +20967,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -20993,13 +20993,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M146" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N146" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -21029,10 +21029,10 @@
         <v>0</v>
       </c>
       <c r="X146" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Y146" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z146" t="n">
         <v>0</v>
@@ -21108,12 +21108,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -21239,7 +21239,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -21249,12 +21249,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -21380,22 +21380,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -21521,7 +21521,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -21531,12 +21531,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Komárno</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Spartak Trnava</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -21662,7 +21662,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -21672,12 +21672,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -21698,13 +21698,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M151" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N151" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -21734,10 +21734,10 @@
         <v>0</v>
       </c>
       <c r="X151" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Y151" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z151" t="n">
         <v>0</v>
@@ -21803,7 +21803,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -21813,12 +21813,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -21944,7 +21944,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -21954,12 +21954,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -22085,7 +22085,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -22095,12 +22095,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -22367,7 +22367,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -22377,12 +22377,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -22508,7 +22508,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -22518,12 +22518,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -22649,7 +22649,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -22659,12 +22659,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -22685,13 +22685,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M158" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N158" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -22721,10 +22721,10 @@
         <v>0</v>
       </c>
       <c r="X158" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Y158" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z158" t="n">
         <v>0</v>
@@ -22800,12 +22800,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -22941,12 +22941,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -23082,12 +23082,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -23354,7 +23354,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -23364,12 +23364,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -23495,7 +23495,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -23505,12 +23505,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -23531,13 +23531,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="M164" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="N164" t="n">
-        <v>3.45</v>
+        <v>5.8</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -23567,16 +23567,16 @@
         <v>0</v>
       </c>
       <c r="X164" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="Y164" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="Z164" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA164" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB164" t="n">
         <v>0</v>
@@ -23918,7 +23918,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -23928,12 +23928,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -23954,13 +23954,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M167" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N167" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -23990,16 +23990,16 @@
         <v>0</v>
       </c>
       <c r="X167" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Y167" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z167" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA167" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB167" t="n">
         <v>0</v>
@@ -24059,7 +24059,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -24069,12 +24069,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -24095,13 +24095,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M168" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N168" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -24131,10 +24131,10 @@
         <v>0</v>
       </c>
       <c r="X168" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Y168" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z168" t="n">
         <v>0</v>
@@ -24200,7 +24200,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -24210,12 +24210,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -24341,7 +24341,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -24351,12 +24351,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -24482,7 +24482,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -24492,12 +24492,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -24518,13 +24518,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M171" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N171" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -24554,10 +24554,10 @@
         <v>0</v>
       </c>
       <c r="X171" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y171" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z171" t="n">
         <v>0</v>
@@ -24623,7 +24623,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -24633,12 +24633,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -24659,13 +24659,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M172" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N172" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -24695,10 +24695,10 @@
         <v>0</v>
       </c>
       <c r="X172" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Y172" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z172" t="n">
         <v>0</v>
@@ -24915,12 +24915,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -25046,22 +25046,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -25187,22 +25187,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -25328,22 +25328,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -25469,7 +25469,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -25479,12 +25479,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -25610,22 +25610,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -25751,7 +25751,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -25761,12 +25761,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -25892,22 +25892,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -26033,7 +26033,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -26043,12 +26043,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -26174,22 +26174,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -26315,22 +26315,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -26456,7 +26456,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -26466,12 +26466,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -26738,7 +26738,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -26748,12 +26748,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -26879,7 +26879,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -26889,12 +26889,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -27020,7 +27020,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -27030,12 +27030,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -27161,7 +27161,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -27171,12 +27171,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -27302,22 +27302,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -27443,7 +27443,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -27453,12 +27453,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -27594,12 +27594,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -27725,7 +27725,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -27735,12 +27735,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -27876,12 +27876,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -28148,7 +28148,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -28158,12 +28158,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -28289,7 +28289,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -28299,12 +28299,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -28430,7 +28430,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -28440,12 +28440,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -28581,12 +28581,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -28712,7 +28712,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -28722,12 +28722,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -28853,7 +28853,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -28863,12 +28863,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -29004,12 +29004,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -29135,22 +29135,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -29276,22 +29276,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -29427,12 +29427,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -29558,22 +29558,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -29594,13 +29594,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M207" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N207" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -29630,10 +29630,10 @@
         <v>0</v>
       </c>
       <c r="X207" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Y207" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z207" t="n">
         <v>0</v>
@@ -29699,7 +29699,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -29709,12 +29709,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -29981,22 +29981,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -30263,7 +30263,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -30273,12 +30273,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -30299,13 +30299,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M212" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N212" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -30335,10 +30335,10 @@
         <v>0</v>
       </c>
       <c r="X212" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Y212" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z212" t="n">
         <v>0</v>
@@ -30545,7 +30545,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -30555,12 +30555,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Kolkheti Poti</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -30696,12 +30696,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -30837,12 +30837,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -30968,22 +30968,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Kolkheti Poti</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -31109,7 +31109,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -31119,12 +31119,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -31260,12 +31260,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -31391,7 +31391,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -31401,12 +31401,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Podbrezová</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -31532,22 +31532,22 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -31673,7 +31673,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -31683,12 +31683,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Podbrezová</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -31814,7 +31814,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -31824,12 +31824,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -31955,7 +31955,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -31965,12 +31965,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -32237,7 +32237,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -32247,12 +32247,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -32378,22 +32378,22 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -32414,13 +32414,13 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="M227" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N227" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -32456,10 +32456,10 @@
         <v>0</v>
       </c>
       <c r="Z227" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA227" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB227" t="n">
         <v>0</v>
@@ -32801,22 +32801,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -32837,13 +32837,13 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="M230" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N230" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O230" t="n">
         <v>0</v>
@@ -32879,10 +32879,10 @@
         <v>0</v>
       </c>
       <c r="Z230" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA230" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB230" t="n">
         <v>0</v>
@@ -33083,7 +33083,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -33093,12 +33093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -33365,7 +33365,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -33375,12 +33375,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -33647,7 +33647,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -33657,12 +33657,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -33929,7 +33929,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -33939,12 +33939,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -34493,7 +34493,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -34503,12 +34503,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -34634,7 +34634,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -34644,12 +34644,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -34775,22 +34775,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -34811,13 +34811,13 @@
         </is>
       </c>
       <c r="L244" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M244" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N244" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="O244" t="n">
         <v>0</v>
@@ -34847,10 +34847,10 @@
         <v>0</v>
       </c>
       <c r="X244" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y244" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z244" t="n">
         <v>0</v>
@@ -34916,22 +34916,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -35067,12 +35067,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -35198,22 +35198,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -35339,22 +35339,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -35480,22 +35480,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -35621,22 +35621,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -35657,13 +35657,13 @@
         </is>
       </c>
       <c r="L250" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M250" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N250" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="O250" t="n">
         <v>0</v>
@@ -35693,10 +35693,10 @@
         <v>0</v>
       </c>
       <c r="X250" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y250" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z250" t="n">
         <v>0</v>
@@ -35772,12 +35772,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -35903,22 +35903,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -36044,22 +36044,22 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -36195,12 +36195,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -36221,13 +36221,13 @@
         </is>
       </c>
       <c r="L254" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="M254" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="N254" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="O254" t="n">
         <v>0</v>
@@ -36257,10 +36257,10 @@
         <v>0</v>
       </c>
       <c r="X254" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="Y254" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Z254" t="n">
         <v>0</v>
@@ -36336,12 +36336,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -36362,13 +36362,13 @@
         </is>
       </c>
       <c r="L255" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="M255" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="N255" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="O255" t="n">
         <v>0</v>
@@ -36398,10 +36398,10 @@
         <v>0</v>
       </c>
       <c r="X255" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="Y255" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Z255" t="n">
         <v>0</v>
@@ -36608,22 +36608,22 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -36749,22 +36749,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -36890,7 +36890,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -36900,12 +36900,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -37031,22 +37031,22 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -37172,22 +37172,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -37313,7 +37313,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -37323,12 +37323,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -37454,22 +37454,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -37736,7 +37736,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -37746,12 +37746,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -37877,22 +37877,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -38159,7 +38159,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -38169,12 +38169,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -38300,22 +38300,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -38451,12 +38451,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -38582,7 +38582,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -38592,12 +38592,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -38723,22 +38723,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -39041,13 +39041,13 @@
         </is>
       </c>
       <c r="L274" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="M274" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="N274" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="O274" t="n">
         <v>0</v>
@@ -39077,10 +39077,10 @@
         <v>0</v>
       </c>
       <c r="X274" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="Y274" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Z274" t="n">
         <v>0</v>
@@ -39428,7 +39428,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -39438,12 +39438,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -39464,13 +39464,13 @@
         </is>
       </c>
       <c r="L277" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M277" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N277" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O277" t="n">
         <v>0</v>
@@ -39500,10 +39500,10 @@
         <v>0</v>
       </c>
       <c r="X277" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Y277" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z277" t="n">
         <v>0</v>
@@ -39569,7 +39569,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -39579,12 +39579,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -39605,13 +39605,13 @@
         </is>
       </c>
       <c r="L278" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M278" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N278" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O278" t="n">
         <v>0</v>
@@ -39641,10 +39641,10 @@
         <v>0</v>
       </c>
       <c r="X278" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Y278" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Z278" t="n">
         <v>0</v>
@@ -39851,7 +39851,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -39861,12 +39861,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -39992,7 +39992,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -40002,12 +40002,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -40133,7 +40133,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -40143,12 +40143,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -40274,7 +40274,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -40284,12 +40284,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -40451,13 +40451,13 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="M284" t="n">
-        <v>4.4</v>
+        <v>4.05</v>
       </c>
       <c r="N284" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="O284" t="n">
         <v>0</v>
@@ -40493,10 +40493,10 @@
         <v>0</v>
       </c>
       <c r="Z284" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AA284" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB284" t="n">
         <v>0</v>
@@ -40556,7 +40556,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -40566,12 +40566,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Wilstermann</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -40592,13 +40592,13 @@
         </is>
       </c>
       <c r="L285" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M285" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N285" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O285" t="n">
         <v>0</v>
@@ -40628,10 +40628,10 @@
         <v>0</v>
       </c>
       <c r="X285" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y285" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z285" t="n">
         <v>0</v>
@@ -40697,7 +40697,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -40707,12 +40707,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Wilstermann</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -40733,13 +40733,13 @@
         </is>
       </c>
       <c r="L286" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M286" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N286" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O286" t="n">
         <v>0</v>
@@ -40769,10 +40769,10 @@
         <v>0</v>
       </c>
       <c r="X286" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y286" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z286" t="n">
         <v>0</v>
@@ -41156,13 +41156,13 @@
         </is>
       </c>
       <c r="L289" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="M289" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="N289" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="O289" t="n">
         <v>0</v>
@@ -41198,10 +41198,10 @@
         <v>0</v>
       </c>
       <c r="Z289" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AA289" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AB289" t="n">
         <v>0</v>

--- a/jogos_2025-08-24.xlsx
+++ b/jogos_2025-08-24.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO290"/>
+  <dimension ref="A1:AO291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1994,10 +1994,10 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,13 +2099,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2135,10 +2135,10 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="M13" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2276,10 +2276,10 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2417,10 +2417,10 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.36</v>
+        <v>5.2</v>
       </c>
       <c r="M15" t="n">
-        <v>3.56</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>2.86</v>
+        <v>1.61</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2558,10 +2558,10 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.01</v>
+        <v>1.78</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.51</v>
+        <v>2.36</v>
       </c>
       <c r="M16" t="n">
-        <v>3.15</v>
+        <v>3.56</v>
       </c>
       <c r="N16" t="n">
-        <v>2.73</v>
+        <v>2.86</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2699,10 +2699,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.78</v>
+        <v>2.01</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -2768,22 +2768,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,13 +2804,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2840,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.16</v>
+        <v>4.3</v>
       </c>
       <c r="M19" t="n">
-        <v>3.27</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>2.16</v>
+        <v>1.66</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3122,10 +3122,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,13 +3227,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.04</v>
+        <v>2.41</v>
       </c>
       <c r="M20" t="n">
-        <v>3.31</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3263,10 +3263,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -3473,22 +3473,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3545,10 +3545,10 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3692,10 +3692,10 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3794,10 +3794,10 @@
         <v>1.28</v>
       </c>
       <c r="M24" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="N24" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
         <v>1.67</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3974,10 +3974,10 @@
         <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -4037,22 +4037,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4109,10 +4109,10 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Taichung Rock</t>
+          <t>Taipower</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Taichung Futuro</t>
+          <t>AC Taipei</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4397,10 +4397,10 @@
         <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4601,22 +4601,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4679,10 +4679,10 @@
         <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4883,22 +4883,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Taiwan Taiwan Football Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Taipower</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AC Taipei</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4919,13 +4919,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4955,10 +4955,10 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
@@ -5024,22 +5024,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5306,22 +5306,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5342,13 +5342,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5447,22 +5447,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Taiwan Taiwan Football Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Taichung Rock</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Taichung Futuro</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5660,10 +5660,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
         <v>0</v>
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5870,22 +5870,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5906,13 +5906,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5942,16 +5942,16 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6047,13 +6047,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -6083,10 +6083,10 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -6152,22 +6152,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6293,22 +6293,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6329,13 +6329,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6365,16 +6365,16 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB42" t="n">
         <v>0</v>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
@@ -6575,22 +6575,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6611,13 +6611,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z44" t="n">
         <v>0</v>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7034,13 +7034,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -7139,22 +7139,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7290,12 +7290,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7316,13 +7316,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -7352,10 +7352,10 @@
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Z49" t="n">
         <v>0</v>
@@ -7421,22 +7421,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Isloch</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitebsk</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7562,22 +7562,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Isloch</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Vitebsk</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7703,7 +7703,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7844,22 +7844,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8021,13 +8021,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -8136,12 +8136,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8559,12 +8559,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9008,13 +9008,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="M61" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="N61" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -9044,16 +9044,16 @@
         <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z61" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
         <v>0</v>
@@ -9123,12 +9123,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9149,13 +9149,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="M62" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="N62" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -9185,16 +9185,16 @@
         <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB62" t="n">
         <v>0</v>
@@ -9431,13 +9431,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -9473,10 +9473,10 @@
         <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB64" t="n">
         <v>0</v>
@@ -9572,13 +9572,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -9677,22 +9677,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9828,12 +9828,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9969,12 +9969,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -10136,13 +10136,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -10172,10 +10172,10 @@
         <v>0</v>
       </c>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z69" t="n">
         <v>0</v>
@@ -10241,7 +10241,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -10277,13 +10277,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.24</v>
+        <v>2.59</v>
       </c>
       <c r="M70" t="n">
-        <v>3.15</v>
+        <v>3.54</v>
       </c>
       <c r="N70" t="n">
-        <v>3.35</v>
+        <v>2.59</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -10313,10 +10313,10 @@
         <v>0</v>
       </c>
       <c r="X70" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="Z70" t="n">
         <v>0</v>
@@ -10382,22 +10382,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -10418,13 +10418,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -10454,10 +10454,10 @@
         <v>0</v>
       </c>
       <c r="X71" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z71" t="n">
         <v>0</v>
@@ -10559,13 +10559,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>6.21</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -10664,7 +10664,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10674,12 +10674,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10700,13 +10700,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10736,10 +10736,10 @@
         <v>0</v>
       </c>
       <c r="X73" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
         <v>0</v>
@@ -11228,7 +11228,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -11238,12 +11238,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -11369,7 +11369,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -11520,12 +11520,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -11542,7 +11542,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L79" t="n">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -11661,12 +11661,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11802,12 +11802,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>UN Käerjéng</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -12074,22 +12074,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>UNA Strassen</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -12356,22 +12356,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -12497,7 +12497,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -12638,22 +12638,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Slutsk</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Neman Grodno</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12779,7 +12779,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12789,12 +12789,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12815,13 +12815,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -12920,7 +12920,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12930,12 +12930,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>UNA Strassen</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -13061,7 +13061,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -13071,12 +13071,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -13093,17 +13093,17 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -13202,22 +13202,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Slutsk</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Neman Grodno</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -13343,7 +13343,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -13353,12 +13353,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>UN Käerjéng</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -13620,27 +13620,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -13752,7 +13752,7 @@
         <v>0</v>
       </c>
       <c r="AO94" s="3" t="n">
-        <v>45893.47916666666</v>
+        <v>45893.45833333334</v>
       </c>
     </row>
     <row r="95">
@@ -13766,7 +13766,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13907,22 +13907,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13943,13 +13943,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -13979,10 +13979,10 @@
         <v>0</v>
       </c>
       <c r="X96" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z96" t="n">
         <v>0</v>
@@ -14048,7 +14048,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -14330,7 +14330,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -14340,12 +14340,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -14481,12 +14481,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -14612,22 +14612,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -14648,13 +14648,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -14684,10 +14684,10 @@
         <v>0</v>
       </c>
       <c r="X101" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z101" t="n">
         <v>0</v>
@@ -14889,12 +14889,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -15021,7 +15021,7 @@
         <v>0</v>
       </c>
       <c r="AO103" s="3" t="n">
-        <v>45893.48958333334</v>
+        <v>45893.47916666666</v>
       </c>
     </row>
     <row r="104">
@@ -15071,13 +15071,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="M104" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="N104" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -15113,10 +15113,10 @@
         <v>0</v>
       </c>
       <c r="Z104" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AA104" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AB104" t="n">
         <v>0</v>
@@ -15171,12 +15171,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -15186,12 +15186,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -15303,7 +15303,7 @@
         <v>0</v>
       </c>
       <c r="AO105" s="3" t="n">
-        <v>45893.5</v>
+        <v>45893.48958333334</v>
       </c>
     </row>
     <row r="106">
@@ -15317,22 +15317,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -15599,7 +15599,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -15609,12 +15609,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -15635,13 +15635,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -15671,10 +15671,10 @@
         <v>0</v>
       </c>
       <c r="X108" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z108" t="n">
         <v>0</v>
@@ -15740,7 +15740,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -15750,12 +15750,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -15881,7 +15881,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -15891,12 +15891,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -16032,12 +16032,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -16163,22 +16163,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -16304,7 +16304,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -16314,12 +16314,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -16455,12 +16455,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -16586,7 +16586,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -16596,12 +16596,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -16727,7 +16727,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -16737,12 +16737,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -16868,7 +16868,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -16878,12 +16878,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -16900,7 +16900,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L117" t="n">
@@ -17009,7 +17009,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -17019,12 +17019,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -17150,7 +17150,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -17160,12 +17160,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -17182,7 +17182,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L119" t="n">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -17301,12 +17301,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -17323,17 +17323,17 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -17363,10 +17363,10 @@
         <v>0</v>
       </c>
       <c r="X120" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y120" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z120" t="n">
         <v>0</v>
@@ -17432,7 +17432,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -17442,12 +17442,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -17573,7 +17573,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -17583,12 +17583,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -17724,12 +17724,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -17855,7 +17855,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -17996,22 +17996,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -18137,22 +18137,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -18169,7 +18169,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L126" t="n">
@@ -18278,7 +18278,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -18288,12 +18288,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -18310,7 +18310,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L127" t="n">
@@ -18419,7 +18419,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -18429,12 +18429,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -18451,7 +18451,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L128" t="n">
@@ -18560,7 +18560,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -18570,12 +18570,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -18711,12 +18711,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -18842,22 +18842,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -18983,7 +18983,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -18993,12 +18993,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Komárno</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Spartak Trnava</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -19265,7 +19265,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -19301,13 +19301,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -19337,10 +19337,10 @@
         <v>0</v>
       </c>
       <c r="X134" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Y134" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z134" t="n">
         <v>0</v>
@@ -19406,7 +19406,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -19416,12 +19416,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -19547,7 +19547,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -19557,12 +19557,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -19688,7 +19688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -19698,12 +19698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -19724,13 +19724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -19760,10 +19760,10 @@
         <v>0</v>
       </c>
       <c r="X137" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Y137" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z137" t="n">
         <v>0</v>
@@ -19829,7 +19829,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -19839,12 +19839,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -19861,7 +19861,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L138" t="n">
@@ -19970,22 +19970,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -20111,22 +20111,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -20143,7 +20143,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L140" t="n">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -20262,12 +20262,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -20393,7 +20393,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -20403,12 +20403,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -20534,7 +20534,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -20544,12 +20544,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -20675,7 +20675,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -20685,12 +20685,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -20816,7 +20816,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -20826,12 +20826,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -20852,13 +20852,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M145" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N145" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -20888,10 +20888,10 @@
         <v>0</v>
       </c>
       <c r="X145" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y145" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z145" t="n">
         <v>0</v>
@@ -20957,7 +20957,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -20967,12 +20967,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -20993,13 +20993,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M146" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N146" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -21029,10 +21029,10 @@
         <v>0</v>
       </c>
       <c r="X146" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Y146" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z146" t="n">
         <v>0</v>
@@ -21098,7 +21098,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -21108,12 +21108,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -21239,7 +21239,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -21249,12 +21249,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -21380,22 +21380,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -21521,7 +21521,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -21531,12 +21531,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Komárno</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Spartak Trnava</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -21662,7 +21662,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -21672,12 +21672,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -21803,7 +21803,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -21813,12 +21813,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -21839,13 +21839,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M152" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -21875,10 +21875,10 @@
         <v>0</v>
       </c>
       <c r="X152" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Y152" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z152" t="n">
         <v>0</v>
@@ -21944,7 +21944,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -21954,12 +21954,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -21980,13 +21980,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M153" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -22016,10 +22016,10 @@
         <v>0</v>
       </c>
       <c r="X153" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y153" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z153" t="n">
         <v>0</v>
@@ -22085,7 +22085,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -22095,12 +22095,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -22367,7 +22367,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -22377,12 +22377,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -22403,13 +22403,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M156" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -22439,10 +22439,10 @@
         <v>0</v>
       </c>
       <c r="X156" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Y156" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z156" t="n">
         <v>0</v>
@@ -22508,7 +22508,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -22518,12 +22518,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -22649,7 +22649,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -22659,12 +22659,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -22785,12 +22785,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -22800,12 +22800,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -22826,13 +22826,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M159" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -22862,10 +22862,10 @@
         <v>0</v>
       </c>
       <c r="X159" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y159" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z159" t="n">
         <v>0</v>
@@ -22917,7 +22917,7 @@
         <v>0</v>
       </c>
       <c r="AO159" s="3" t="n">
-        <v>45893.51041666666</v>
+        <v>45893.5</v>
       </c>
     </row>
     <row r="160">
@@ -22967,13 +22967,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="M160" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N160" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -23003,10 +23003,10 @@
         <v>0</v>
       </c>
       <c r="X160" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y160" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z160" t="n">
         <v>0</v>
@@ -23108,13 +23108,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M161" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N161" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -23144,10 +23144,10 @@
         <v>0</v>
       </c>
       <c r="X161" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y161" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z161" t="n">
         <v>0</v>
@@ -23208,27 +23208,27 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -23249,13 +23249,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M162" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N162" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -23285,10 +23285,10 @@
         <v>0</v>
       </c>
       <c r="X162" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Y162" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z162" t="n">
         <v>0</v>
@@ -23340,7 +23340,7 @@
         <v>0</v>
       </c>
       <c r="AO162" s="3" t="n">
-        <v>45893.51736111111</v>
+        <v>45893.51041666666</v>
       </c>
     </row>
     <row r="163">
@@ -23349,27 +23349,27 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -23481,7 +23481,7 @@
         <v>0</v>
       </c>
       <c r="AO163" s="3" t="n">
-        <v>45893.52083333334</v>
+        <v>45893.51736111111</v>
       </c>
     </row>
     <row r="164">
@@ -23495,7 +23495,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -23505,12 +23505,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -23531,13 +23531,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="M164" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="N164" t="n">
-        <v>5.8</v>
+        <v>3.45</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -23567,16 +23567,16 @@
         <v>0</v>
       </c>
       <c r="X164" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="Y164" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="Z164" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA164" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB164" t="n">
         <v>0</v>
@@ -23636,7 +23636,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -23646,12 +23646,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -23777,7 +23777,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -23787,12 +23787,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -23918,7 +23918,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -23928,12 +23928,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -23954,13 +23954,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M167" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N167" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -23990,16 +23990,16 @@
         <v>0</v>
       </c>
       <c r="X167" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Y167" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z167" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA167" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB167" t="n">
         <v>0</v>
@@ -24059,7 +24059,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -24069,12 +24069,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -24095,13 +24095,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M168" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N168" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -24131,10 +24131,10 @@
         <v>0</v>
       </c>
       <c r="X168" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Y168" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z168" t="n">
         <v>0</v>
@@ -24200,7 +24200,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -24210,12 +24210,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -24236,13 +24236,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M169" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N169" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -24272,10 +24272,10 @@
         <v>0</v>
       </c>
       <c r="X169" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y169" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z169" t="n">
         <v>0</v>
@@ -24341,7 +24341,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -24351,12 +24351,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -24377,13 +24377,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M170" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N170" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -24413,10 +24413,10 @@
         <v>0</v>
       </c>
       <c r="X170" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Y170" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z170" t="n">
         <v>0</v>
@@ -24482,7 +24482,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -24492,12 +24492,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -24623,7 +24623,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -24633,12 +24633,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -24759,12 +24759,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -24774,12 +24774,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -24891,7 +24891,7 @@
         <v>0</v>
       </c>
       <c r="AO173" s="3" t="n">
-        <v>45893.53125</v>
+        <v>45893.52083333334</v>
       </c>
     </row>
     <row r="174">
@@ -24900,12 +24900,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -24915,12 +24915,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -25032,7 +25032,7 @@
         <v>0</v>
       </c>
       <c r="AO174" s="3" t="n">
-        <v>45893.54166666666</v>
+        <v>45893.53125</v>
       </c>
     </row>
     <row r="175">
@@ -25046,22 +25046,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -25187,22 +25187,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -25328,7 +25328,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -25338,12 +25338,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -25610,22 +25610,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -25751,22 +25751,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -25892,22 +25892,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -26033,7 +26033,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -26043,12 +26043,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -26174,7 +26174,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -26184,12 +26184,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -26315,7 +26315,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -26325,12 +26325,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -26456,7 +26456,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -26466,12 +26466,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -26607,12 +26607,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -26738,22 +26738,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -26879,7 +26879,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -26889,12 +26889,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -27020,7 +27020,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -27030,12 +27030,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -27171,12 +27171,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -27302,7 +27302,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -27312,12 +27312,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -27584,7 +27584,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -27594,12 +27594,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -27725,7 +27725,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -27735,12 +27735,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -27876,12 +27876,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -28017,12 +28017,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -28148,7 +28148,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -28158,12 +28158,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -28289,7 +28289,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -28299,12 +28299,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -28430,7 +28430,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -28440,12 +28440,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -28722,12 +28722,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -28853,7 +28853,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -28863,12 +28863,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -29135,22 +29135,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -29276,22 +29276,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -29417,7 +29417,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -29427,12 +29427,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -29553,27 +29553,27 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -29685,7 +29685,7 @@
         <v>0</v>
       </c>
       <c r="AO207" s="3" t="n">
-        <v>45893.5625</v>
+        <v>45893.54166666666</v>
       </c>
     </row>
     <row r="208">
@@ -29699,7 +29699,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -29709,12 +29709,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -29735,13 +29735,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M208" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N208" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -29771,10 +29771,10 @@
         <v>0</v>
       </c>
       <c r="X208" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Y208" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z208" t="n">
         <v>0</v>
@@ -29840,7 +29840,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -29850,12 +29850,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -29876,13 +29876,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M209" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N209" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -29912,10 +29912,10 @@
         <v>0</v>
       </c>
       <c r="X209" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y209" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z209" t="n">
         <v>0</v>
@@ -29981,22 +29981,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -30122,7 +30122,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -30132,12 +30132,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -30158,13 +30158,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M211" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N211" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -30194,10 +30194,10 @@
         <v>0</v>
       </c>
       <c r="X211" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y211" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z211" t="n">
         <v>0</v>
@@ -30263,7 +30263,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -30273,12 +30273,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -30299,13 +30299,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M212" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N212" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -30335,10 +30335,10 @@
         <v>0</v>
       </c>
       <c r="X212" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Y212" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z212" t="n">
         <v>0</v>
@@ -30399,12 +30399,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -30414,12 +30414,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -30440,13 +30440,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="M213" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N213" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -30476,16 +30476,16 @@
         <v>0</v>
       </c>
       <c r="X213" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Y213" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z213" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA213" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB213" t="n">
         <v>0</v>
@@ -30531,7 +30531,7 @@
         <v>0</v>
       </c>
       <c r="AO213" s="3" t="n">
-        <v>45893.57291666666</v>
+        <v>45893.5625</v>
       </c>
     </row>
     <row r="214">
@@ -30540,27 +30540,27 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Kolkheti Poti</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -30581,13 +30581,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M214" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N214" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -30617,16 +30617,16 @@
         <v>0</v>
       </c>
       <c r="X214" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Y214" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z214" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA214" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB214" t="n">
         <v>0</v>
@@ -30672,7 +30672,7 @@
         <v>0</v>
       </c>
       <c r="AO214" s="3" t="n">
-        <v>45893.58333333334</v>
+        <v>45893.57291666666</v>
       </c>
     </row>
     <row r="215">
@@ -30686,22 +30686,22 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -30827,22 +30827,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -30968,7 +30968,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -30978,12 +30978,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -31109,22 +31109,22 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Kolkheti Poti</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -31391,7 +31391,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -31401,12 +31401,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Podbrezová</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -31532,22 +31532,22 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -31673,22 +31673,22 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Podbrezová</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -31814,7 +31814,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -31824,12 +31824,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -31991,13 +31991,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M224" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N224" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -32237,7 +32237,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -32247,12 +32247,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -32273,13 +32273,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M226" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N226" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -32373,27 +32373,27 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -32505,7 +32505,7 @@
         <v>0</v>
       </c>
       <c r="AO227" s="3" t="n">
-        <v>45893.59375</v>
+        <v>45893.58333333334</v>
       </c>
     </row>
     <row r="228">
@@ -32519,7 +32519,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -32529,12 +32529,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -32555,13 +32555,13 @@
         </is>
       </c>
       <c r="L228" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M228" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N228" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O228" t="n">
         <v>0</v>
@@ -32591,10 +32591,10 @@
         <v>0</v>
       </c>
       <c r="X228" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Y228" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Z228" t="n">
         <v>0</v>
@@ -32660,7 +32660,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -32670,12 +32670,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -32696,13 +32696,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M229" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N229" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -32732,10 +32732,10 @@
         <v>0</v>
       </c>
       <c r="X229" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Y229" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Z229" t="n">
         <v>0</v>
@@ -32937,27 +32937,27 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -33069,7 +33069,7 @@
         <v>0</v>
       </c>
       <c r="AO231" s="3" t="n">
-        <v>45893.60416666666</v>
+        <v>45893.59375</v>
       </c>
     </row>
     <row r="232">
@@ -33083,7 +33083,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -33093,12 +33093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -33224,7 +33224,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -33234,12 +33234,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -33506,7 +33506,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -33516,12 +33516,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -33642,12 +33642,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -33657,12 +33657,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -33774,7 +33774,7 @@
         <v>0</v>
       </c>
       <c r="AO236" s="3" t="n">
-        <v>45893.625</v>
+        <v>45893.60416666666</v>
       </c>
     </row>
     <row r="237">
@@ -33798,12 +33798,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -33939,12 +33939,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -34070,22 +34070,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -34106,13 +34106,13 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="M239" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="N239" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="O239" t="n">
         <v>0</v>
@@ -34142,10 +34142,10 @@
         <v>0</v>
       </c>
       <c r="X239" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Y239" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Z239" t="n">
         <v>0</v>
@@ -34211,22 +34211,22 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>CD El Nacional</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -34352,7 +34352,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -34362,12 +34362,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>CD El Nacional</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -34488,12 +34488,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -34503,12 +34503,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -34529,13 +34529,13 @@
         </is>
       </c>
       <c r="L242" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="M242" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="N242" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="O242" t="n">
         <v>0</v>
@@ -34565,10 +34565,10 @@
         <v>0</v>
       </c>
       <c r="X242" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Y242" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Z242" t="n">
         <v>0</v>
@@ -34620,7 +34620,7 @@
         <v>0</v>
       </c>
       <c r="AO242" s="3" t="n">
-        <v>45893.63541666666</v>
+        <v>45893.625</v>
       </c>
     </row>
     <row r="243">
@@ -34634,7 +34634,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -34644,12 +34644,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -34770,12 +34770,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -34785,12 +34785,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -34811,13 +34811,13 @@
         </is>
       </c>
       <c r="L244" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M244" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N244" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="O244" t="n">
         <v>0</v>
@@ -34847,10 +34847,10 @@
         <v>0</v>
       </c>
       <c r="X244" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y244" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z244" t="n">
         <v>0</v>
@@ -34902,7 +34902,7 @@
         <v>0</v>
       </c>
       <c r="AO244" s="3" t="n">
-        <v>45893.64583333334</v>
+        <v>45893.63541666666</v>
       </c>
     </row>
     <row r="245">
@@ -34916,22 +34916,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -35067,12 +35067,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -35208,12 +35208,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -35339,7 +35339,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -35349,12 +35349,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -35480,22 +35480,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -35631,12 +35631,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -35772,12 +35772,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -35903,7 +35903,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -35913,12 +35913,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -35939,13 +35939,13 @@
         </is>
       </c>
       <c r="L252" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M252" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N252" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="O252" t="n">
         <v>0</v>
@@ -35975,10 +35975,10 @@
         <v>0</v>
       </c>
       <c r="X252" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y252" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z252" t="n">
         <v>0</v>
@@ -36044,22 +36044,22 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -36180,27 +36180,27 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -36221,13 +36221,13 @@
         </is>
       </c>
       <c r="L254" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M254" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N254" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="O254" t="n">
         <v>0</v>
@@ -36257,10 +36257,10 @@
         <v>0</v>
       </c>
       <c r="X254" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Y254" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z254" t="n">
         <v>0</v>
@@ -36312,7 +36312,7 @@
         <v>0</v>
       </c>
       <c r="AO254" s="3" t="n">
-        <v>45893.65625</v>
+        <v>45893.64583333334</v>
       </c>
     </row>
     <row r="255">
@@ -36503,13 +36503,13 @@
         </is>
       </c>
       <c r="L256" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M256" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N256" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O256" t="n">
         <v>0</v>
@@ -36539,10 +36539,10 @@
         <v>0</v>
       </c>
       <c r="X256" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Y256" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z256" t="n">
         <v>0</v>
@@ -36603,12 +36603,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -36618,12 +36618,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -36644,13 +36644,13 @@
         </is>
       </c>
       <c r="L257" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M257" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N257" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="O257" t="n">
         <v>0</v>
@@ -36680,10 +36680,10 @@
         <v>0</v>
       </c>
       <c r="X257" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Y257" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z257" t="n">
         <v>0</v>
@@ -36735,7 +36735,7 @@
         <v>0</v>
       </c>
       <c r="AO257" s="3" t="n">
-        <v>45893.66666666666</v>
+        <v>45893.65625</v>
       </c>
     </row>
     <row r="258">
@@ -36749,7 +36749,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -36759,12 +36759,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -36785,13 +36785,13 @@
         </is>
       </c>
       <c r="L258" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M258" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N258" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="O258" t="n">
         <v>0</v>
@@ -36890,22 +36890,22 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -37031,7 +37031,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -37041,12 +37041,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -37067,13 +37067,13 @@
         </is>
       </c>
       <c r="L260" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M260" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N260" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O260" t="n">
         <v>0</v>
@@ -37103,10 +37103,10 @@
         <v>0</v>
       </c>
       <c r="X260" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y260" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z260" t="n">
         <v>0</v>
@@ -37313,7 +37313,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -37323,12 +37323,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -37454,7 +37454,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -37464,12 +37464,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -37595,22 +37595,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -37631,13 +37631,13 @@
         </is>
       </c>
       <c r="L264" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M264" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N264" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O264" t="n">
         <v>0</v>
@@ -37667,10 +37667,10 @@
         <v>0</v>
       </c>
       <c r="X264" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y264" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z264" t="n">
         <v>0</v>
@@ -37772,13 +37772,13 @@
         </is>
       </c>
       <c r="L265" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M265" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N265" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O265" t="n">
         <v>0</v>
@@ -37877,22 +37877,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -38018,7 +38018,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -38028,12 +38028,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -38054,13 +38054,13 @@
         </is>
       </c>
       <c r="L267" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M267" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N267" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O267" t="n">
         <v>0</v>
@@ -38084,16 +38084,16 @@
         <v>0</v>
       </c>
       <c r="V267" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W267" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="X267" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Y267" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z267" t="n">
         <v>0</v>
@@ -38159,7 +38159,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -38169,12 +38169,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -38295,27 +38295,27 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -38336,13 +38336,13 @@
         </is>
       </c>
       <c r="L269" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M269" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N269" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O269" t="n">
         <v>0</v>
@@ -38366,16 +38366,16 @@
         <v>0</v>
       </c>
       <c r="V269" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W269" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="X269" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y269" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z269" t="n">
         <v>0</v>
@@ -38427,7 +38427,7 @@
         <v>0</v>
       </c>
       <c r="AO269" s="3" t="n">
-        <v>45893.6875</v>
+        <v>45893.66666666666</v>
       </c>
     </row>
     <row r="270">
@@ -38582,22 +38582,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -38723,22 +38723,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -38859,27 +38859,27 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -38991,7 +38991,7 @@
         <v>0</v>
       </c>
       <c r="AO273" s="3" t="n">
-        <v>45893.70833333334</v>
+        <v>45893.6875</v>
       </c>
     </row>
     <row r="274">
@@ -39005,7 +39005,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -39015,12 +39015,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -39041,13 +39041,13 @@
         </is>
       </c>
       <c r="L274" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M274" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N274" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O274" t="n">
         <v>0</v>
@@ -39077,10 +39077,10 @@
         <v>0</v>
       </c>
       <c r="X274" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Y274" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z274" t="n">
         <v>0</v>
@@ -39141,12 +39141,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -39156,12 +39156,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -39182,13 +39182,13 @@
         </is>
       </c>
       <c r="L275" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M275" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N275" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O275" t="n">
         <v>0</v>
@@ -39218,10 +39218,10 @@
         <v>0</v>
       </c>
       <c r="X275" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Y275" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z275" t="n">
         <v>0</v>
@@ -39273,7 +39273,7 @@
         <v>0</v>
       </c>
       <c r="AO275" s="3" t="n">
-        <v>45893.72916666666</v>
+        <v>45893.70833333334</v>
       </c>
     </row>
     <row r="276">
@@ -39282,12 +39282,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -39297,12 +39297,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -39414,7 +39414,7 @@
         <v>0</v>
       </c>
       <c r="AO276" s="3" t="n">
-        <v>45893.76041666666</v>
+        <v>45893.72916666666</v>
       </c>
     </row>
     <row r="277">
@@ -39423,12 +39423,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -39438,12 +39438,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -39464,13 +39464,13 @@
         </is>
       </c>
       <c r="L277" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M277" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N277" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O277" t="n">
         <v>0</v>
@@ -39500,10 +39500,10 @@
         <v>0</v>
       </c>
       <c r="X277" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Y277" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z277" t="n">
         <v>0</v>
@@ -39555,7 +39555,7 @@
         <v>0</v>
       </c>
       <c r="AO277" s="3" t="n">
-        <v>45893.77083333334</v>
+        <v>45893.76041666666</v>
       </c>
     </row>
     <row r="278">
@@ -39846,12 +39846,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -39861,12 +39861,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -39887,13 +39887,13 @@
         </is>
       </c>
       <c r="L280" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M280" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N280" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O280" t="n">
         <v>0</v>
@@ -39923,10 +39923,10 @@
         <v>0</v>
       </c>
       <c r="X280" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Y280" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z280" t="n">
         <v>0</v>
@@ -39978,7 +39978,7 @@
         <v>0</v>
       </c>
       <c r="AO280" s="3" t="n">
-        <v>45893.83333333334</v>
+        <v>45893.77083333334</v>
       </c>
     </row>
     <row r="281">
@@ -39992,7 +39992,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -40002,12 +40002,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -40133,7 +40133,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -40143,12 +40143,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -40274,7 +40274,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -40284,12 +40284,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -40310,13 +40310,13 @@
         </is>
       </c>
       <c r="L283" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M283" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N283" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O283" t="n">
         <v>0</v>
@@ -40352,10 +40352,10 @@
         <v>0</v>
       </c>
       <c r="Z283" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA283" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB283" t="n">
         <v>0</v>
@@ -40415,7 +40415,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -40425,12 +40425,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -40451,13 +40451,13 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M284" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N284" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O284" t="n">
         <v>0</v>
@@ -40493,10 +40493,10 @@
         <v>0</v>
       </c>
       <c r="Z284" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA284" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB284" t="n">
         <v>0</v>
@@ -40551,12 +40551,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -40566,12 +40566,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Wilstermann</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="AO285" s="3" t="n">
-        <v>45893.85416666666</v>
+        <v>45893.83333333334</v>
       </c>
     </row>
     <row r="286">
@@ -40697,7 +40697,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -40707,12 +40707,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Wilstermann</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -40733,13 +40733,13 @@
         </is>
       </c>
       <c r="L286" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M286" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N286" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O286" t="n">
         <v>0</v>
@@ -40769,10 +40769,10 @@
         <v>0</v>
       </c>
       <c r="X286" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y286" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z286" t="n">
         <v>0</v>
@@ -40833,12 +40833,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -40848,12 +40848,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -40874,13 +40874,13 @@
         </is>
       </c>
       <c r="L287" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M287" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N287" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O287" t="n">
         <v>0</v>
@@ -40910,10 +40910,10 @@
         <v>0</v>
       </c>
       <c r="X287" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y287" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z287" t="n">
         <v>0</v>
@@ -40965,7 +40965,7 @@
         <v>0</v>
       </c>
       <c r="AO287" s="3" t="n">
-        <v>45893.875</v>
+        <v>45893.85416666666</v>
       </c>
     </row>
     <row r="288">
@@ -40974,12 +40974,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -40989,12 +40989,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -41106,7 +41106,7 @@
         <v>0</v>
       </c>
       <c r="AO288" s="3" t="n">
-        <v>45893.90625</v>
+        <v>45893.875</v>
       </c>
     </row>
     <row r="289">
@@ -41115,12 +41115,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>22:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -41130,12 +41130,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -41156,13 +41156,13 @@
         </is>
       </c>
       <c r="L289" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M289" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N289" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O289" t="n">
         <v>0</v>
@@ -41198,10 +41198,10 @@
         <v>0</v>
       </c>
       <c r="Z289" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA289" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB289" t="n">
         <v>0</v>
@@ -41247,7 +41247,7 @@
         <v>0</v>
       </c>
       <c r="AO289" s="3" t="n">
-        <v>45893.92708333334</v>
+        <v>45893.90625</v>
       </c>
     </row>
     <row r="290">
@@ -41256,138 +41256,279 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
+          <t>22:15</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Sporting KC</t>
+        </is>
+      </c>
+      <c r="G290" t="n">
+        <v>0</v>
+      </c>
+      <c r="H290" t="n">
+        <v>0</v>
+      </c>
+      <c r="I290" t="n">
+        <v>0</v>
+      </c>
+      <c r="J290" t="n">
+        <v>0</v>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L290" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M290" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="N290" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O290" t="n">
+        <v>0</v>
+      </c>
+      <c r="P290" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q290" t="n">
+        <v>0</v>
+      </c>
+      <c r="R290" t="n">
+        <v>0</v>
+      </c>
+      <c r="S290" t="n">
+        <v>0</v>
+      </c>
+      <c r="T290" t="n">
+        <v>0</v>
+      </c>
+      <c r="U290" t="n">
+        <v>0</v>
+      </c>
+      <c r="V290" t="n">
+        <v>0</v>
+      </c>
+      <c r="W290" t="n">
+        <v>0</v>
+      </c>
+      <c r="X290" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y290" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z290" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA290" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD290" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE290" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO290" s="3" t="n">
+        <v>45893.92708333334</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="n">
+        <v>45893</v>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="C290" t="inlineStr">
+      <c r="C291" t="inlineStr">
         <is>
           <t>USA MLS Next Pro</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr">
+      <c r="D291" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E290" t="inlineStr">
+      <c r="E291" t="inlineStr">
         <is>
           <t>Real Monarchs</t>
         </is>
       </c>
-      <c r="F290" t="inlineStr">
+      <c r="F291" t="inlineStr">
         <is>
           <t>Minnesota United II</t>
         </is>
       </c>
-      <c r="G290" t="n">
-        <v>0</v>
-      </c>
-      <c r="H290" t="n">
-        <v>0</v>
-      </c>
-      <c r="I290" t="n">
-        <v>0</v>
-      </c>
-      <c r="J290" t="n">
-        <v>0</v>
-      </c>
-      <c r="K290" t="inlineStr">
+      <c r="G291" t="n">
+        <v>0</v>
+      </c>
+      <c r="H291" t="n">
+        <v>0</v>
+      </c>
+      <c r="I291" t="n">
+        <v>0</v>
+      </c>
+      <c r="J291" t="n">
+        <v>0</v>
+      </c>
+      <c r="K291" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L290" t="n">
-        <v>0</v>
-      </c>
-      <c r="M290" t="n">
-        <v>0</v>
-      </c>
-      <c r="N290" t="n">
-        <v>0</v>
-      </c>
-      <c r="O290" t="n">
-        <v>0</v>
-      </c>
-      <c r="P290" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q290" t="n">
-        <v>0</v>
-      </c>
-      <c r="R290" t="n">
-        <v>0</v>
-      </c>
-      <c r="S290" t="n">
-        <v>0</v>
-      </c>
-      <c r="T290" t="n">
-        <v>0</v>
-      </c>
-      <c r="U290" t="n">
-        <v>0</v>
-      </c>
-      <c r="V290" t="n">
-        <v>0</v>
-      </c>
-      <c r="W290" t="n">
-        <v>0</v>
-      </c>
-      <c r="X290" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y290" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z290" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA290" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB290" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC290" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD290" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE290" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF290" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG290" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH290" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI290" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ290" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK290" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL290" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM290" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN290" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO290" s="3" t="n">
+      <c r="L291" t="n">
+        <v>0</v>
+      </c>
+      <c r="M291" t="n">
+        <v>0</v>
+      </c>
+      <c r="N291" t="n">
+        <v>0</v>
+      </c>
+      <c r="O291" t="n">
+        <v>0</v>
+      </c>
+      <c r="P291" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q291" t="n">
+        <v>0</v>
+      </c>
+      <c r="R291" t="n">
+        <v>0</v>
+      </c>
+      <c r="S291" t="n">
+        <v>0</v>
+      </c>
+      <c r="T291" t="n">
+        <v>0</v>
+      </c>
+      <c r="U291" t="n">
+        <v>0</v>
+      </c>
+      <c r="V291" t="n">
+        <v>0</v>
+      </c>
+      <c r="W291" t="n">
+        <v>0</v>
+      </c>
+      <c r="X291" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y291" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD291" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE291" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO291" s="3" t="n">
         <v>45893.9375</v>
       </c>
     </row>

--- a/jogos_2025-08-24.xlsx
+++ b/jogos_2025-08-24.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ming Chuan University</t>
+          <t>Tatung</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hang Yuen FC</t>
+          <t>Tainan City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tatung</t>
+          <t>Ming Chuan University</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tainan City</t>
+          <t>Hang Yuen FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,13 +2099,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2135,10 +2135,10 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2276,10 +2276,10 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2417,10 +2417,10 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.2</v>
+        <v>2.36</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>3.56</v>
       </c>
       <c r="N15" t="n">
-        <v>1.61</v>
+        <v>2.86</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2558,10 +2558,10 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.78</v>
+        <v>2.01</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.36</v>
+        <v>3.1</v>
       </c>
       <c r="M16" t="n">
-        <v>3.56</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>2.86</v>
+        <v>2.2</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2699,10 +2699,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.01</v>
+        <v>1.84</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -2768,22 +2768,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,13 +2804,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,13 +2945,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2981,10 +2981,10 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="M19" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="N19" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3122,10 +3122,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Y19" t="n">
         <v>1.78</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.92</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,13 +3227,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.41</v>
+        <v>4.3</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="N20" t="n">
-        <v>2.7</v>
+        <v>1.66</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3263,10 +3263,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3404,10 +3404,10 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
@@ -3473,22 +3473,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3545,10 +3545,10 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3692,10 +3692,10 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3974,10 +3974,10 @@
         <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -4037,22 +4037,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Taiwan Taiwan Football Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Taipower</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AC Taipei</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Taiwan Taiwan Football Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Taichung Rock</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Taichung Futuro</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4601,22 +4601,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Taiwan Taiwan Football Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Taipower</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>AC Taipei</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4679,10 +4679,10 @@
         <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
@@ -4742,22 +4742,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4919,13 +4919,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.71</v>
+        <v>3.25</v>
       </c>
       <c r="M32" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="N32" t="n">
-        <v>4.2</v>
+        <v>2.01</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4955,10 +4955,10 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
@@ -5024,22 +5024,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5060,13 +5060,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5102,10 +5102,10 @@
         <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5306,22 +5306,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5342,13 +5342,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5447,22 +5447,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Taiwan Taiwan Football Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Taichung Rock</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Taichung Futuro</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5483,13 +5483,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5519,10 +5519,10 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z36" t="n">
         <v>0</v>
@@ -5588,22 +5588,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6047,13 +6047,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -6152,22 +6152,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6188,13 +6188,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -6224,10 +6224,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6329,13 +6329,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6365,16 +6365,16 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
         <v>0</v>
@@ -6444,12 +6444,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="M43" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N43" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6506,16 +6506,16 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB43" t="n">
         <v>0</v>
@@ -6585,12 +6585,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6611,13 +6611,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="M44" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="N44" t="n">
-        <v>4.1</v>
+        <v>2.75</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6650,7 +6650,7 @@
         <v>1.7</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="Z44" t="n">
         <v>0</v>
@@ -6867,12 +6867,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6998,22 +6998,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7034,13 +7034,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -7139,22 +7139,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7175,13 +7175,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7290,12 +7290,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7316,13 +7316,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -7352,10 +7352,10 @@
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
         <v>0</v>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7562,22 +7562,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Isloch</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitebsk</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7598,13 +7598,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7844,22 +7844,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7985,22 +7985,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8021,13 +8021,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.94</v>
+        <v>3.74</v>
       </c>
       <c r="M54" t="n">
-        <v>3.72</v>
+        <v>3.9</v>
       </c>
       <c r="N54" t="n">
-        <v>3.73</v>
+        <v>1.89</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -8057,10 +8057,10 @@
         <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -8136,12 +8136,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8408,22 +8408,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Isloch</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Vitebsk</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8559,12 +8559,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9008,13 +9008,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="M61" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="N61" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -9044,16 +9044,16 @@
         <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB61" t="n">
         <v>0</v>
@@ -9123,12 +9123,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9149,13 +9149,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="M62" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="N62" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -9185,16 +9185,16 @@
         <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z62" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
         <v>0</v>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9713,13 +9713,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>6.21</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9828,12 +9828,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9854,13 +9854,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9890,10 +9890,10 @@
         <v>0</v>
       </c>
       <c r="X67" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z67" t="n">
         <v>0</v>
@@ -9959,7 +9959,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9969,12 +9969,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -10136,13 +10136,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.24</v>
+        <v>2.59</v>
       </c>
       <c r="M69" t="n">
-        <v>3.15</v>
+        <v>3.54</v>
       </c>
       <c r="N69" t="n">
-        <v>3.35</v>
+        <v>2.59</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -10172,10 +10172,10 @@
         <v>0</v>
       </c>
       <c r="X69" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="Z69" t="n">
         <v>0</v>
@@ -10241,7 +10241,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -10277,13 +10277,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.59</v>
+        <v>2.24</v>
       </c>
       <c r="M70" t="n">
-        <v>3.54</v>
+        <v>3.15</v>
       </c>
       <c r="N70" t="n">
-        <v>2.59</v>
+        <v>3.35</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -10313,10 +10313,10 @@
         <v>0</v>
       </c>
       <c r="X70" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="Z70" t="n">
         <v>0</v>
@@ -10382,22 +10382,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -10418,13 +10418,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -10454,10 +10454,10 @@
         <v>0</v>
       </c>
       <c r="X71" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
         <v>0</v>
@@ -10523,22 +10523,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10559,13 +10559,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>6.21</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -10664,22 +10664,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10805,22 +10805,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -11238,12 +11238,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -11520,12 +11520,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -11542,7 +11542,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L79" t="n">
@@ -11651,22 +11651,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11802,12 +11802,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>UN Käerjéng</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11933,7 +11933,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11943,12 +11943,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -12074,22 +12074,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -12215,7 +12215,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -12356,7 +12356,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -12388,7 +12388,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L85" t="n">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -12638,22 +12638,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12789,12 +12789,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -13061,7 +13061,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -13071,12 +13071,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -13097,13 +13097,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -13202,22 +13202,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Slutsk</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Neman Grodno</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -13343,7 +13343,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -13353,12 +13353,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>UN Käerjéng</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -13484,7 +13484,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -13494,12 +13494,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Slutsk</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Neman Grodno</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -13635,12 +13635,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -13661,13 +13661,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -13766,7 +13766,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13917,12 +13917,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13943,13 +13943,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -13979,10 +13979,10 @@
         <v>0</v>
       </c>
       <c r="X96" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z96" t="n">
         <v>0</v>
@@ -14048,7 +14048,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -14261,10 +14261,10 @@
         <v>0</v>
       </c>
       <c r="X98" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z98" t="n">
         <v>0</v>
@@ -14330,7 +14330,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -14340,12 +14340,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -14481,12 +14481,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -14622,12 +14622,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -14894,22 +14894,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -15317,22 +15317,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -15458,7 +15458,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -15468,12 +15468,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ironi Ramat HaSharon</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -15599,7 +15599,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -15609,12 +15609,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -15740,7 +15740,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -15750,12 +15750,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -15881,7 +15881,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -15891,12 +15891,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15913,7 +15913,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L110" t="n">
@@ -16022,7 +16022,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -16032,12 +16032,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -16163,22 +16163,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -16304,7 +16304,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -16314,12 +16314,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -16445,7 +16445,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -16455,12 +16455,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -16586,7 +16586,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -16596,12 +16596,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Komárno</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Spartak Trnava</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -16737,12 +16737,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -16868,7 +16868,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -16878,12 +16878,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -16904,13 +16904,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -16940,10 +16940,10 @@
         <v>0</v>
       </c>
       <c r="X117" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Y117" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z117" t="n">
         <v>0</v>
@@ -17019,12 +17019,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -17150,7 +17150,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -17160,12 +17160,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -17182,7 +17182,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L119" t="n">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -17301,12 +17301,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -17323,17 +17323,17 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -17363,10 +17363,10 @@
         <v>0</v>
       </c>
       <c r="X120" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z120" t="n">
         <v>0</v>
@@ -17432,7 +17432,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -17442,12 +17442,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -17464,7 +17464,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L121" t="n">
@@ -17573,7 +17573,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -17583,12 +17583,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -17605,7 +17605,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L122" t="n">
@@ -17714,22 +17714,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -17746,7 +17746,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L123" t="n">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -17996,22 +17996,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -18137,7 +18137,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -18147,12 +18147,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -18169,7 +18169,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L126" t="n">
@@ -18278,7 +18278,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -18288,12 +18288,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -18310,7 +18310,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L127" t="n">
@@ -18419,7 +18419,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -18429,12 +18429,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -18451,7 +18451,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L128" t="n">
@@ -18560,7 +18560,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -18570,12 +18570,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Ironi Ramat HaSharon</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -18701,7 +18701,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -18711,12 +18711,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -18842,7 +18842,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -18852,12 +18852,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -18983,7 +18983,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -18993,12 +18993,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Komárno</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Spartak Trnava</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -19265,7 +19265,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -19406,7 +19406,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -19416,12 +19416,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -19547,22 +19547,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -19579,7 +19579,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L136" t="n">
@@ -19688,22 +19688,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -19839,12 +19839,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -19980,12 +19980,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -20006,13 +20006,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -20042,10 +20042,10 @@
         <v>0</v>
       </c>
       <c r="X139" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y139" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z139" t="n">
         <v>0</v>
@@ -20121,12 +20121,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -20262,12 +20262,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -20393,7 +20393,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -20403,12 +20403,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -20534,7 +20534,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -20544,12 +20544,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -20570,13 +20570,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M143" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -20606,10 +20606,10 @@
         <v>0</v>
       </c>
       <c r="X143" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y143" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z143" t="n">
         <v>0</v>
@@ -20675,7 +20675,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -20685,12 +20685,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -20816,7 +20816,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -20826,12 +20826,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -20957,7 +20957,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -20967,12 +20967,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -21098,7 +21098,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -21108,12 +21108,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -21134,13 +21134,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M147" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N147" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -21170,10 +21170,10 @@
         <v>0</v>
       </c>
       <c r="X147" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Y147" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z147" t="n">
         <v>0</v>
@@ -21239,7 +21239,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -21249,12 +21249,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -21390,12 +21390,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -21531,12 +21531,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -21662,7 +21662,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -21672,12 +21672,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -21803,7 +21803,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -21813,12 +21813,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -21839,13 +21839,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -21875,10 +21875,10 @@
         <v>0</v>
       </c>
       <c r="X152" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Y152" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z152" t="n">
         <v>0</v>
@@ -21944,7 +21944,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -21954,12 +21954,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -21980,13 +21980,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -22016,10 +22016,10 @@
         <v>0</v>
       </c>
       <c r="X153" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y153" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z153" t="n">
         <v>0</v>
@@ -22085,7 +22085,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -22095,12 +22095,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -22367,7 +22367,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -22377,12 +22377,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -22403,13 +22403,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M156" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N156" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -22439,10 +22439,10 @@
         <v>0</v>
       </c>
       <c r="X156" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Y156" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z156" t="n">
         <v>0</v>
@@ -22508,7 +22508,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -22518,12 +22518,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -22649,7 +22649,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -22659,12 +22659,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -22790,7 +22790,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -22800,12 +22800,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -22826,13 +22826,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="M159" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="N159" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -22862,10 +22862,10 @@
         <v>0</v>
       </c>
       <c r="X159" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="Y159" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="Z159" t="n">
         <v>0</v>
@@ -23082,12 +23082,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -23108,13 +23108,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>1.89</v>
+        <v>2.11</v>
       </c>
       <c r="M161" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N161" t="n">
-        <v>4.06</v>
+        <v>3.5</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -23144,10 +23144,10 @@
         <v>0</v>
       </c>
       <c r="X161" t="n">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="Y161" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="Z161" t="n">
         <v>0</v>
@@ -23223,12 +23223,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -23249,13 +23249,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>2.11</v>
+        <v>1.89</v>
       </c>
       <c r="M162" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N162" t="n">
-        <v>3.5</v>
+        <v>4.06</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -23285,10 +23285,10 @@
         <v>0</v>
       </c>
       <c r="X162" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="Y162" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="Z162" t="n">
         <v>0</v>
@@ -23495,7 +23495,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -23505,12 +23505,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -23531,13 +23531,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M164" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N164" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -23567,16 +23567,16 @@
         <v>0</v>
       </c>
       <c r="X164" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Y164" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z164" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA164" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB164" t="n">
         <v>0</v>
@@ -23636,7 +23636,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -23646,12 +23646,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -23672,13 +23672,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M165" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N165" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -23708,10 +23708,10 @@
         <v>0</v>
       </c>
       <c r="X165" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Y165" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z165" t="n">
         <v>0</v>
@@ -23777,7 +23777,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -23787,12 +23787,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -24059,7 +24059,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -24069,12 +24069,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -24095,13 +24095,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M168" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N168" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -24131,10 +24131,10 @@
         <v>0</v>
       </c>
       <c r="X168" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y168" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z168" t="n">
         <v>0</v>
@@ -24200,7 +24200,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -24210,12 +24210,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -24236,13 +24236,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="M169" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="N169" t="n">
-        <v>5.8</v>
+        <v>3.45</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -24272,16 +24272,16 @@
         <v>0</v>
       </c>
       <c r="X169" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="Y169" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="Z169" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA169" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB169" t="n">
         <v>0</v>
@@ -24341,7 +24341,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -24351,12 +24351,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -24377,13 +24377,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M170" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N170" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -24413,10 +24413,10 @@
         <v>0</v>
       </c>
       <c r="X170" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Y170" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z170" t="n">
         <v>0</v>
@@ -24492,12 +24492,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -24623,7 +24623,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -24633,12 +24633,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -24764,7 +24764,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -24774,12 +24774,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -25046,22 +25046,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -25187,7 +25187,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -25197,12 +25197,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -25328,22 +25328,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -25610,22 +25610,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -25751,7 +25751,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -25761,12 +25761,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -25892,22 +25892,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -26033,22 +26033,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -26174,22 +26174,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -26315,7 +26315,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -26325,12 +26325,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -26456,7 +26456,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -26466,12 +26466,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -26597,7 +26597,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -26607,12 +26607,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -26738,22 +26738,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -26879,7 +26879,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -26889,12 +26889,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -27020,7 +27020,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -27030,12 +27030,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -27171,12 +27171,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -27302,7 +27302,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -27312,12 +27312,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -27443,7 +27443,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -27453,12 +27453,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -27584,7 +27584,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -27594,12 +27594,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -27725,7 +27725,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -27735,12 +27735,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -28007,7 +28007,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -28017,12 +28017,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -28158,12 +28158,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -28289,7 +28289,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -28299,12 +28299,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -28430,7 +28430,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -28440,12 +28440,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -28571,7 +28571,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -28581,12 +28581,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -28712,7 +28712,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -28722,12 +28722,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -28853,7 +28853,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -28863,12 +28863,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -29004,12 +29004,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -29135,22 +29135,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -29276,7 +29276,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -29286,12 +29286,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -29417,7 +29417,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -29427,12 +29427,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -29558,7 +29558,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -29568,12 +29568,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -29699,7 +29699,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -29709,12 +29709,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -29735,13 +29735,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M208" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N208" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -29771,10 +29771,10 @@
         <v>0</v>
       </c>
       <c r="X208" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Y208" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z208" t="n">
         <v>0</v>
@@ -29850,12 +29850,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -29876,13 +29876,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>3.15</v>
+        <v>2.55</v>
       </c>
       <c r="M209" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N209" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -29912,10 +29912,10 @@
         <v>0</v>
       </c>
       <c r="X209" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="Y209" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="Z209" t="n">
         <v>0</v>
@@ -29981,22 +29981,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -30122,22 +30122,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -30404,7 +30404,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -30414,12 +30414,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -30440,13 +30440,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M213" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N213" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -30476,10 +30476,10 @@
         <v>0</v>
       </c>
       <c r="X213" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y213" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z213" t="n">
         <v>0</v>
@@ -30686,7 +30686,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -30696,12 +30696,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Kolkheti Poti</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -30827,22 +30827,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -30968,7 +30968,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -30978,12 +30978,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -31004,13 +31004,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M217" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N217" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -31109,22 +31109,22 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Kolkheti Poti</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -31250,7 +31250,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -31260,12 +31260,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Podbrezová</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -31391,7 +31391,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -31401,12 +31401,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Podbrezová</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -31532,22 +31532,22 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -31673,22 +31673,22 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -31814,7 +31814,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -31824,12 +31824,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -31850,13 +31850,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M223" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N223" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -31955,7 +31955,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -31965,12 +31965,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -31991,13 +31991,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M224" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N224" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -32096,7 +32096,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -32106,12 +32106,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -32237,7 +32237,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -32247,12 +32247,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -32273,13 +32273,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M226" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N226" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -32378,7 +32378,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -32519,22 +32519,22 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -32555,13 +32555,13 @@
         </is>
       </c>
       <c r="L228" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M228" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N228" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O228" t="n">
         <v>0</v>
@@ -32591,10 +32591,10 @@
         <v>0</v>
       </c>
       <c r="X228" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Y228" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Z228" t="n">
         <v>0</v>
@@ -32660,7 +32660,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -32670,12 +32670,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -32696,13 +32696,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M229" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N229" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -32732,10 +32732,10 @@
         <v>0</v>
       </c>
       <c r="X229" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Y229" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Z229" t="n">
         <v>0</v>
@@ -32801,7 +32801,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -32811,12 +32811,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -32837,13 +32837,13 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="M230" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N230" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="O230" t="n">
         <v>0</v>
@@ -32879,10 +32879,10 @@
         <v>0</v>
       </c>
       <c r="Z230" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA230" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB230" t="n">
         <v>0</v>
@@ -32942,22 +32942,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -32978,13 +32978,13 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="M231" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N231" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O231" t="n">
         <v>0</v>
@@ -33020,10 +33020,10 @@
         <v>0</v>
       </c>
       <c r="Z231" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA231" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB231" t="n">
         <v>0</v>
@@ -33224,7 +33224,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -33234,12 +33234,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -33506,7 +33506,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -33516,12 +33516,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -33798,12 +33798,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -33929,22 +33929,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -34070,7 +34070,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -34080,12 +34080,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>CD El Nacional</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -34211,7 +34211,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -34221,12 +34221,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -34352,22 +34352,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>CD El Nacional</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -34388,13 +34388,13 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="M241" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="N241" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="O241" t="n">
         <v>0</v>
@@ -34424,10 +34424,10 @@
         <v>0</v>
       </c>
       <c r="X241" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Y241" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Z241" t="n">
         <v>0</v>
@@ -34493,7 +34493,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -34503,12 +34503,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -34529,13 +34529,13 @@
         </is>
       </c>
       <c r="L242" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="M242" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="N242" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="O242" t="n">
         <v>0</v>
@@ -34565,10 +34565,10 @@
         <v>0</v>
       </c>
       <c r="X242" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Y242" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Z242" t="n">
         <v>0</v>
@@ -34926,12 +34926,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -35057,22 +35057,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -35208,12 +35208,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -35339,7 +35339,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -35349,12 +35349,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -35480,22 +35480,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -35631,12 +35631,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -35772,12 +35772,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -36195,12 +36195,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -36326,7 +36326,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -36336,12 +36336,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -36362,13 +36362,13 @@
         </is>
       </c>
       <c r="L255" t="n">
-        <v>1.4</v>
+        <v>2.85</v>
       </c>
       <c r="M255" t="n">
-        <v>4.9</v>
+        <v>3.45</v>
       </c>
       <c r="N255" t="n">
-        <v>7.2</v>
+        <v>2.38</v>
       </c>
       <c r="O255" t="n">
         <v>0</v>
@@ -36398,10 +36398,10 @@
         <v>0</v>
       </c>
       <c r="X255" t="n">
-        <v>1.63</v>
+        <v>1.84</v>
       </c>
       <c r="Y255" t="n">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="Z255" t="n">
         <v>0</v>
@@ -36467,7 +36467,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -36477,12 +36477,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -36503,13 +36503,13 @@
         </is>
       </c>
       <c r="L256" t="n">
-        <v>2.85</v>
+        <v>1.4</v>
       </c>
       <c r="M256" t="n">
-        <v>3.45</v>
+        <v>4.9</v>
       </c>
       <c r="N256" t="n">
-        <v>2.38</v>
+        <v>7.2</v>
       </c>
       <c r="O256" t="n">
         <v>0</v>
@@ -36539,10 +36539,10 @@
         <v>0</v>
       </c>
       <c r="X256" t="n">
-        <v>1.84</v>
+        <v>1.63</v>
       </c>
       <c r="Y256" t="n">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="Z256" t="n">
         <v>0</v>
@@ -36749,7 +36749,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -36759,12 +36759,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -36785,13 +36785,13 @@
         </is>
       </c>
       <c r="L258" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M258" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N258" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="O258" t="n">
         <v>0</v>
@@ -36890,7 +36890,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -36900,12 +36900,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -37031,7 +37031,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -37041,12 +37041,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -37067,13 +37067,13 @@
         </is>
       </c>
       <c r="L260" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M260" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N260" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O260" t="n">
         <v>0</v>
@@ -37103,10 +37103,10 @@
         <v>0</v>
       </c>
       <c r="X260" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y260" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z260" t="n">
         <v>0</v>
@@ -37172,22 +37172,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -37313,7 +37313,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -37323,12 +37323,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -37454,7 +37454,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -37464,12 +37464,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -37490,13 +37490,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M263" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N263" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -37520,16 +37520,16 @@
         <v>0</v>
       </c>
       <c r="V263" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W263" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="X263" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y263" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z263" t="n">
         <v>0</v>
@@ -37605,12 +37605,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -37746,12 +37746,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -37772,13 +37772,13 @@
         </is>
       </c>
       <c r="L265" t="n">
-        <v>2.21</v>
+        <v>2.37</v>
       </c>
       <c r="M265" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N265" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="O265" t="n">
         <v>0</v>
@@ -37877,7 +37877,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -37887,12 +37887,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -38018,22 +38018,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -38159,22 +38159,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -38195,13 +38195,13 @@
         </is>
       </c>
       <c r="L268" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M268" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N268" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O268" t="n">
         <v>0</v>
@@ -38231,10 +38231,10 @@
         <v>0</v>
       </c>
       <c r="X268" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y268" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z268" t="n">
         <v>0</v>
@@ -38300,22 +38300,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -38336,13 +38336,13 @@
         </is>
       </c>
       <c r="L269" t="n">
-        <v>2.46</v>
+        <v>2.21</v>
       </c>
       <c r="M269" t="n">
         <v>3.15</v>
       </c>
       <c r="N269" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="O269" t="n">
         <v>0</v>
@@ -38366,16 +38366,16 @@
         <v>0</v>
       </c>
       <c r="V269" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W269" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="X269" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Y269" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z269" t="n">
         <v>0</v>
@@ -38441,22 +38441,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -38582,22 +38582,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -38723,22 +38723,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -38864,22 +38864,22 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -39005,7 +39005,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -39015,12 +39015,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -39041,13 +39041,13 @@
         </is>
       </c>
       <c r="L274" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M274" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N274" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O274" t="n">
         <v>0</v>
@@ -39077,10 +39077,10 @@
         <v>0</v>
       </c>
       <c r="X274" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Y274" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z274" t="n">
         <v>0</v>
@@ -39146,7 +39146,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -39156,12 +39156,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -39182,13 +39182,13 @@
         </is>
       </c>
       <c r="L275" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M275" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N275" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O275" t="n">
         <v>0</v>
@@ -39218,10 +39218,10 @@
         <v>0</v>
       </c>
       <c r="X275" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Y275" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z275" t="n">
         <v>0</v>
@@ -40002,12 +40002,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -40133,7 +40133,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -40143,12 +40143,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -40169,13 +40169,13 @@
         </is>
       </c>
       <c r="L282" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M282" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N282" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O282" t="n">
         <v>0</v>
@@ -40211,10 +40211,10 @@
         <v>0</v>
       </c>
       <c r="Z282" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA282" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB282" t="n">
         <v>0</v>
@@ -40274,7 +40274,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -40284,12 +40284,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -40310,13 +40310,13 @@
         </is>
       </c>
       <c r="L283" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M283" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N283" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O283" t="n">
         <v>0</v>
@@ -40352,10 +40352,10 @@
         <v>0</v>
       </c>
       <c r="Z283" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA283" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB283" t="n">
         <v>0</v>
@@ -40566,12 +40566,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G285" t="n">

--- a/jogos_2025-08-24.xlsx
+++ b/jogos_2025-08-24.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="M15" t="n">
-        <v>3.56</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2558,10 +2558,10 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="M16" t="n">
         <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,13 +2804,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="M17" t="n">
-        <v>3.3</v>
+        <v>3.56</v>
       </c>
       <c r="N17" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2840,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,13 +2945,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2981,10 +2981,10 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>5.2</v>
+        <v>2.41</v>
       </c>
       <c r="M19" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>1.61</v>
+        <v>2.7</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3122,10 +3122,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,13 +3227,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="M20" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="N20" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3263,10 +3263,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Y20" t="n">
         <v>1.78</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.92</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="N21" t="n">
-        <v>2.7</v>
+        <v>1.66</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3404,10 +3404,10 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="M22" t="n">
         <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3692,10 +3692,10 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3974,10 +3974,10 @@
         <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -4037,22 +4037,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Taiwan Taiwan Football Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Taichung Rock</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Taichung Futuro</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,13 +4496,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4601,22 +4601,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Taiwan Taiwan Football Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Taipower</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AC Taipei</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4679,10 +4679,10 @@
         <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
@@ -4742,22 +4742,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4883,22 +4883,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Taiwan Taiwan Football Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Taichung Rock</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Taichung Futuro</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4919,13 +4919,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5060,13 +5060,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.48</v>
+        <v>1.71</v>
       </c>
       <c r="M33" t="n">
-        <v>5</v>
+        <v>3.85</v>
       </c>
       <c r="N33" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5096,16 +5096,16 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Taiwan Taiwan Football Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Taipower</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>AC Taipei</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5306,22 +5306,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5447,22 +5447,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5483,13 +5483,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5519,10 +5519,10 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
         <v>0</v>
@@ -5588,22 +5588,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5870,22 +5870,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5906,13 +5906,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5942,10 +5942,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6047,13 +6047,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.15</v>
+        <v>2.6</v>
       </c>
       <c r="M40" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N40" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -6083,16 +6083,16 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB40" t="n">
         <v>0</v>
@@ -6152,22 +6152,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6188,13 +6188,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -6224,10 +6224,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6506,16 +6506,16 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
         <v>0</v>
@@ -6585,12 +6585,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6611,13 +6611,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="M44" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="N44" t="n">
-        <v>2.75</v>
+        <v>4.1</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6650,7 +6650,7 @@
         <v>1.7</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="Z44" t="n">
         <v>0</v>
@@ -6857,22 +6857,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6998,22 +6998,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7034,13 +7034,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7175,13 +7175,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -7280,22 +7280,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7316,13 +7316,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -7421,22 +7421,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7562,22 +7562,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7598,13 +7598,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7844,22 +7844,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7916,10 +7916,10 @@
         <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Z53" t="n">
         <v>0</v>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7995,12 +7995,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8021,13 +8021,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -8057,10 +8057,10 @@
         <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>
@@ -8126,22 +8126,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8267,22 +8267,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9008,13 +9008,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="M61" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="N61" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -9044,16 +9044,16 @@
         <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z61" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
         <v>0</v>
@@ -9113,22 +9113,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9149,13 +9149,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.58</v>
+        <v>4.9</v>
       </c>
       <c r="M62" t="n">
-        <v>4.2</v>
+        <v>4.34</v>
       </c>
       <c r="N62" t="n">
-        <v>5.5</v>
+        <v>1.62</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -9185,16 +9185,16 @@
         <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB62" t="n">
         <v>0</v>
@@ -9395,22 +9395,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -9431,13 +9431,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>4.9</v>
+        <v>1.52</v>
       </c>
       <c r="M64" t="n">
-        <v>4.34</v>
+        <v>4.6</v>
       </c>
       <c r="N64" t="n">
-        <v>1.62</v>
+        <v>5.6</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -9473,7 +9473,7 @@
         <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AA64" t="n">
         <v>1.62</v>
@@ -9677,22 +9677,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9713,13 +9713,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.46</v>
+        <v>2.24</v>
       </c>
       <c r="M66" t="n">
-        <v>4.65</v>
+        <v>3.15</v>
       </c>
       <c r="N66" t="n">
-        <v>6.21</v>
+        <v>3.35</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9749,10 +9749,10 @@
         <v>0</v>
       </c>
       <c r="X66" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z66" t="n">
         <v>0</v>
@@ -9818,22 +9818,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9854,13 +9854,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.75</v>
+        <v>1.46</v>
       </c>
       <c r="M67" t="n">
-        <v>3.25</v>
+        <v>4.65</v>
       </c>
       <c r="N67" t="n">
-        <v>2.55</v>
+        <v>6.21</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9890,10 +9890,10 @@
         <v>0</v>
       </c>
       <c r="X67" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
         <v>0</v>
@@ -9959,22 +9959,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -10277,13 +10277,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -10313,10 +10313,10 @@
         <v>0</v>
       </c>
       <c r="X70" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
         <v>0</v>
@@ -10382,22 +10382,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -10418,13 +10418,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -10454,10 +10454,10 @@
         <v>0</v>
       </c>
       <c r="X71" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z71" t="n">
         <v>0</v>
@@ -11238,12 +11238,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>UN Käerjéng</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -11369,7 +11369,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>UNA Strassen</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -11510,22 +11510,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -11651,22 +11651,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11802,12 +11802,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>UN Käerjéng</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11943,12 +11943,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -12215,22 +12215,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -12356,7 +12356,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -12388,7 +12388,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L85" t="n">
@@ -12497,7 +12497,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -12638,22 +12638,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12779,7 +12779,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12789,12 +12789,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12920,7 +12920,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12930,12 +12930,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>UNA Strassen</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -13061,7 +13061,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -13071,12 +13071,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -13097,13 +13097,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -13202,22 +13202,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Slutsk</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Neman Grodno</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -13343,7 +13343,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -13353,12 +13353,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -13375,7 +13375,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L92" t="n">
@@ -13484,22 +13484,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Slutsk</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Neman Grodno</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -13635,12 +13635,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -13661,13 +13661,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -13766,7 +13766,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13917,12 +13917,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -14048,22 +14048,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -14261,10 +14261,10 @@
         <v>0</v>
       </c>
       <c r="X98" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z98" t="n">
         <v>0</v>
@@ -14330,22 +14330,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -14612,22 +14612,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -14753,22 +14753,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -14789,13 +14789,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -14825,10 +14825,10 @@
         <v>0</v>
       </c>
       <c r="X102" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Y102" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z102" t="n">
         <v>0</v>
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -15458,7 +15458,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -15468,12 +15468,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -15599,7 +15599,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -15609,12 +15609,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -15750,12 +15750,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -15881,7 +15881,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -15891,12 +15891,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Komárno</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Spartak Trnava</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -15913,7 +15913,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L110" t="n">
@@ -16022,7 +16022,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -16032,12 +16032,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -16054,7 +16054,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L111" t="n">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -16173,12 +16173,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -16304,7 +16304,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -16314,12 +16314,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -16445,7 +16445,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -16455,12 +16455,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Ironi Ramat HaSharon</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -16586,7 +16586,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -16596,12 +16596,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Komárno</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spartak Trnava</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -16727,7 +16727,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -16737,12 +16737,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -16868,7 +16868,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -16878,12 +16878,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -16904,13 +16904,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>4.3</v>
+        <v>1.7</v>
       </c>
       <c r="M117" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="N117" t="n">
-        <v>1.85</v>
+        <v>5</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -16940,10 +16940,10 @@
         <v>0</v>
       </c>
       <c r="X117" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="Y117" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Z117" t="n">
         <v>0</v>
@@ -17009,7 +17009,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -17019,12 +17019,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -17150,7 +17150,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -17160,12 +17160,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -17301,12 +17301,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -17323,7 +17323,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L120" t="n">
@@ -17432,7 +17432,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -17442,12 +17442,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -17464,7 +17464,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L121" t="n">
@@ -17573,7 +17573,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -17583,12 +17583,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -17605,17 +17605,17 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -17645,10 +17645,10 @@
         <v>0</v>
       </c>
       <c r="X122" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y122" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z122" t="n">
         <v>0</v>
@@ -17714,22 +17714,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -17855,7 +17855,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -17865,12 +17865,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -17891,13 +17891,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -17927,10 +17927,10 @@
         <v>0</v>
       </c>
       <c r="X124" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y124" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z124" t="n">
         <v>0</v>
@@ -17996,7 +17996,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -18006,12 +18006,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -18137,22 +18137,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -18278,7 +18278,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -18288,12 +18288,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -18314,13 +18314,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -18350,10 +18350,10 @@
         <v>0</v>
       </c>
       <c r="X127" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y127" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z127" t="n">
         <v>0</v>
@@ -18419,22 +18419,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -18570,12 +18570,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Ironi Ramat HaSharon</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -18842,7 +18842,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -18852,12 +18852,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -18983,22 +18983,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -19265,7 +19265,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -19406,22 +19406,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -19688,22 +19688,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -19980,12 +19980,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -20006,13 +20006,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -20042,10 +20042,10 @@
         <v>0</v>
       </c>
       <c r="X139" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Y139" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z139" t="n">
         <v>0</v>
@@ -20121,12 +20121,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -20262,12 +20262,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -20393,7 +20393,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -20403,12 +20403,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -20534,7 +20534,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -20544,12 +20544,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -20570,13 +20570,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M143" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N143" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -20606,10 +20606,10 @@
         <v>0</v>
       </c>
       <c r="X143" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y143" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z143" t="n">
         <v>0</v>
@@ -20675,7 +20675,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -20685,12 +20685,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -20816,7 +20816,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -20826,12 +20826,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -20957,7 +20957,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -20967,12 +20967,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -20993,13 +20993,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M146" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N146" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -21029,10 +21029,10 @@
         <v>0</v>
       </c>
       <c r="X146" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Y146" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z146" t="n">
         <v>0</v>
@@ -21098,7 +21098,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -21108,12 +21108,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -21134,13 +21134,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N147" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -21170,10 +21170,10 @@
         <v>0</v>
       </c>
       <c r="X147" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Y147" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z147" t="n">
         <v>0</v>
@@ -21390,12 +21390,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -21521,7 +21521,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -21531,12 +21531,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -21662,7 +21662,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -21672,12 +21672,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -21803,7 +21803,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -21813,12 +21813,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -21944,7 +21944,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -21954,12 +21954,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -21976,7 +21976,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L153" t="n">
@@ -22085,7 +22085,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -22095,12 +22095,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -22367,7 +22367,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -22377,12 +22377,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -22508,7 +22508,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -22518,12 +22518,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -22540,7 +22540,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L157" t="n">
@@ -22649,7 +22649,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -22659,12 +22659,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -22790,7 +22790,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -22800,12 +22800,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -22822,17 +22822,17 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L159" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M159" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N159" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -22862,10 +22862,10 @@
         <v>0</v>
       </c>
       <c r="X159" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y159" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z159" t="n">
         <v>0</v>
@@ -22941,12 +22941,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -22967,13 +22967,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>3.64</v>
+        <v>1.89</v>
       </c>
       <c r="M160" t="n">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="N160" t="n">
-        <v>2.01</v>
+        <v>4.06</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -23223,12 +23223,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -23249,13 +23249,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>1.89</v>
+        <v>3.64</v>
       </c>
       <c r="M162" t="n">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="N162" t="n">
-        <v>4.06</v>
+        <v>2.01</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -23495,7 +23495,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -23505,12 +23505,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -23636,7 +23636,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -23646,12 +23646,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -23672,13 +23672,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M165" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N165" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -23708,10 +23708,10 @@
         <v>0</v>
       </c>
       <c r="X165" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Y165" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z165" t="n">
         <v>0</v>
@@ -23777,7 +23777,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -23787,12 +23787,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -23813,13 +23813,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M166" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N166" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -23849,10 +23849,10 @@
         <v>0</v>
       </c>
       <c r="X166" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y166" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z166" t="n">
         <v>0</v>
@@ -23918,7 +23918,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -23928,12 +23928,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -24059,7 +24059,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -24069,12 +24069,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -24095,13 +24095,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M168" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N168" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -24131,10 +24131,10 @@
         <v>0</v>
       </c>
       <c r="X168" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y168" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z168" t="n">
         <v>0</v>
@@ -24341,7 +24341,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -24351,12 +24351,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -24492,12 +24492,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -24623,7 +24623,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -24633,12 +24633,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -24764,7 +24764,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -24774,12 +24774,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -24800,13 +24800,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M173" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N173" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -24836,10 +24836,10 @@
         <v>0</v>
       </c>
       <c r="X173" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Y173" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z173" t="n">
         <v>0</v>
@@ -25046,22 +25046,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -25328,7 +25328,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -25338,12 +25338,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -25469,22 +25469,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -25610,7 +25610,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -25620,12 +25620,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -25751,22 +25751,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -25892,22 +25892,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -26174,22 +26174,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -26315,22 +26315,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -26456,7 +26456,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -26466,12 +26466,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -26597,7 +26597,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -26607,12 +26607,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -26738,7 +26738,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -26748,12 +26748,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -26879,7 +26879,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -26889,12 +26889,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -27020,22 +27020,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -27161,7 +27161,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -27171,12 +27171,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -27312,12 +27312,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -27453,12 +27453,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -27584,7 +27584,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -27594,12 +27594,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -28007,7 +28007,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -28017,12 +28017,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -28158,12 +28158,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -28289,7 +28289,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -28299,12 +28299,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -28430,7 +28430,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -28440,12 +28440,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -28571,7 +28571,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -28581,12 +28581,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -28712,7 +28712,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -28722,12 +28722,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -28853,7 +28853,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -28863,12 +28863,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -29004,12 +29004,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -29135,7 +29135,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -29145,12 +29145,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -29286,12 +29286,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -29417,22 +29417,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -29558,7 +29558,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -29568,12 +29568,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -29699,7 +29699,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -29709,12 +29709,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -29840,22 +29840,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -29876,13 +29876,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M209" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N209" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -29912,10 +29912,10 @@
         <v>0</v>
       </c>
       <c r="X209" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Y209" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z209" t="n">
         <v>0</v>
@@ -29981,7 +29981,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -29991,12 +29991,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -30122,22 +30122,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -30158,13 +30158,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M211" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N211" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -30194,10 +30194,10 @@
         <v>0</v>
       </c>
       <c r="X211" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y211" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z211" t="n">
         <v>0</v>
@@ -30414,12 +30414,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -30440,13 +30440,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>3.15</v>
+        <v>2.55</v>
       </c>
       <c r="M213" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N213" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -30476,10 +30476,10 @@
         <v>0</v>
       </c>
       <c r="X213" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="Y213" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="Z213" t="n">
         <v>0</v>
@@ -30686,22 +30686,22 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Kolkheti Poti</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -30827,22 +30827,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -30968,7 +30968,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -30978,12 +30978,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -31004,13 +31004,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M217" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N217" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -31109,22 +31109,22 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -31250,7 +31250,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -31260,12 +31260,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Podbrezová</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -31391,7 +31391,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -31401,12 +31401,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -31427,13 +31427,13 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M220" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N220" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -31683,12 +31683,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -31814,22 +31814,22 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Kolkheti Poti</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -31850,13 +31850,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M223" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N223" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -31965,12 +31965,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -32096,7 +32096,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -32106,12 +32106,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -32132,13 +32132,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M225" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N225" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -32378,7 +32378,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Podbrezová</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -32519,22 +32519,22 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -32555,13 +32555,13 @@
         </is>
       </c>
       <c r="L228" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M228" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N228" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O228" t="n">
         <v>0</v>
@@ -32591,10 +32591,10 @@
         <v>0</v>
       </c>
       <c r="X228" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Y228" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Z228" t="n">
         <v>0</v>
@@ -32660,7 +32660,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -32670,12 +32670,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -32696,13 +32696,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>1.21</v>
+        <v>7.5</v>
       </c>
       <c r="M229" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="N229" t="n">
-        <v>11</v>
+        <v>1.28</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -32732,16 +32732,16 @@
         <v>0</v>
       </c>
       <c r="X229" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Y229" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Z229" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA229" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB229" t="n">
         <v>0</v>
@@ -32801,22 +32801,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -32942,7 +32942,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -32952,12 +32952,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -32978,13 +32978,13 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="M231" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N231" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="O231" t="n">
         <v>0</v>
@@ -33020,10 +33020,10 @@
         <v>0</v>
       </c>
       <c r="Z231" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA231" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB231" t="n">
         <v>0</v>
@@ -33083,7 +33083,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -33093,12 +33093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -33365,7 +33365,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -33375,12 +33375,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -33788,22 +33788,22 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>CD El Nacional</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -33929,22 +33929,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -34070,22 +34070,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>CD El Nacional</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -34106,13 +34106,13 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="M239" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="N239" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="O239" t="n">
         <v>0</v>
@@ -34142,10 +34142,10 @@
         <v>0</v>
       </c>
       <c r="X239" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Y239" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Z239" t="n">
         <v>0</v>
@@ -34352,7 +34352,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -34362,12 +34362,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -34388,13 +34388,13 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="M241" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="N241" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="O241" t="n">
         <v>0</v>
@@ -34424,10 +34424,10 @@
         <v>0</v>
       </c>
       <c r="X241" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Y241" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Z241" t="n">
         <v>0</v>
@@ -34493,22 +34493,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -34926,12 +34926,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -35057,22 +35057,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -35198,22 +35198,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -35339,22 +35339,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -35490,12 +35490,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -35621,22 +35621,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -35657,13 +35657,13 @@
         </is>
       </c>
       <c r="L250" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M250" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N250" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="O250" t="n">
         <v>0</v>
@@ -35693,10 +35693,10 @@
         <v>0</v>
       </c>
       <c r="X250" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y250" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z250" t="n">
         <v>0</v>
@@ -35762,22 +35762,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -35903,22 +35903,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -35939,13 +35939,13 @@
         </is>
       </c>
       <c r="L252" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M252" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N252" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="O252" t="n">
         <v>0</v>
@@ -35975,10 +35975,10 @@
         <v>0</v>
       </c>
       <c r="X252" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y252" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z252" t="n">
         <v>0</v>
@@ -36054,12 +36054,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -36195,12 +36195,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -36477,12 +36477,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -36503,13 +36503,13 @@
         </is>
       </c>
       <c r="L256" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="M256" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="N256" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="O256" t="n">
         <v>0</v>
@@ -36539,10 +36539,10 @@
         <v>0</v>
       </c>
       <c r="X256" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="Y256" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Z256" t="n">
         <v>0</v>
@@ -36618,12 +36618,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -36644,13 +36644,13 @@
         </is>
       </c>
       <c r="L257" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="M257" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="N257" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="O257" t="n">
         <v>0</v>
@@ -36680,10 +36680,10 @@
         <v>0</v>
       </c>
       <c r="X257" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="Y257" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Z257" t="n">
         <v>0</v>
@@ -36759,12 +36759,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -36890,7 +36890,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -36900,12 +36900,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -37031,22 +37031,22 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -37172,7 +37172,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -37182,12 +37182,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -37313,22 +37313,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -37349,13 +37349,13 @@
         </is>
       </c>
       <c r="L262" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="M262" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N262" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O262" t="n">
         <v>0</v>
@@ -37379,16 +37379,16 @@
         <v>0</v>
       </c>
       <c r="V262" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W262" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="X262" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y262" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z262" t="n">
         <v>0</v>
@@ -37464,12 +37464,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -37490,13 +37490,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>2.46</v>
+        <v>1.73</v>
       </c>
       <c r="M263" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="N263" t="n">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -37520,16 +37520,16 @@
         <v>0</v>
       </c>
       <c r="V263" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W263" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="X263" t="n">
-        <v>2.53</v>
+        <v>2.25</v>
       </c>
       <c r="Y263" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="Z263" t="n">
         <v>0</v>
@@ -37595,7 +37595,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -37605,12 +37605,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -37631,13 +37631,13 @@
         </is>
       </c>
       <c r="L264" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M264" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N264" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="O264" t="n">
         <v>0</v>
@@ -37736,7 +37736,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -37746,12 +37746,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -37772,13 +37772,13 @@
         </is>
       </c>
       <c r="L265" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M265" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N265" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="O265" t="n">
         <v>0</v>
@@ -38028,12 +38028,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -38159,7 +38159,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -38169,12 +38169,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -38195,13 +38195,13 @@
         </is>
       </c>
       <c r="L268" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M268" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N268" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O268" t="n">
         <v>0</v>
@@ -38231,10 +38231,10 @@
         <v>0</v>
       </c>
       <c r="X268" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y268" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z268" t="n">
         <v>0</v>
@@ -38441,22 +38441,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -38582,7 +38582,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -38592,12 +38592,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -38864,22 +38864,22 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -39569,7 +39569,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -39579,12 +39579,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -39605,13 +39605,13 @@
         </is>
       </c>
       <c r="L278" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M278" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N278" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O278" t="n">
         <v>0</v>
@@ -39641,10 +39641,10 @@
         <v>0</v>
       </c>
       <c r="X278" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Y278" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z278" t="n">
         <v>0</v>
@@ -39710,7 +39710,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -39720,12 +39720,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -39746,13 +39746,13 @@
         </is>
       </c>
       <c r="L279" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="M279" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N279" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O279" t="n">
         <v>0</v>
@@ -39782,10 +39782,10 @@
         <v>0</v>
       </c>
       <c r="X279" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Y279" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z279" t="n">
         <v>0</v>
@@ -39861,12 +39861,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -39887,13 +39887,13 @@
         </is>
       </c>
       <c r="L280" t="n">
-        <v>2.08</v>
+        <v>4.7</v>
       </c>
       <c r="M280" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="N280" t="n">
-        <v>3.55</v>
+        <v>1.71</v>
       </c>
       <c r="O280" t="n">
         <v>0</v>
@@ -40274,7 +40274,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -40284,12 +40284,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -40415,7 +40415,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -40425,12 +40425,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -40556,7 +40556,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -40566,12 +40566,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -40697,7 +40697,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -40707,12 +40707,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Wilstermann</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -40733,13 +40733,13 @@
         </is>
       </c>
       <c r="L286" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M286" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N286" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O286" t="n">
         <v>0</v>
@@ -40769,10 +40769,10 @@
         <v>0</v>
       </c>
       <c r="X286" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y286" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z286" t="n">
         <v>0</v>
@@ -40838,7 +40838,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -40848,12 +40848,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Wilstermann</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -40874,13 +40874,13 @@
         </is>
       </c>
       <c r="L287" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M287" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N287" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O287" t="n">
         <v>0</v>
@@ -40910,10 +40910,10 @@
         <v>0</v>
       </c>
       <c r="X287" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y287" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z287" t="n">
         <v>0</v>

--- a/jogos_2025-08-24.xlsx
+++ b/jogos_2025-08-24.xlsx
@@ -663,12 +663,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -804,12 +804,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,13 +2099,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2135,10 +2135,10 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.32</v>
+        <v>5.2</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>2.87</v>
+        <v>1.61</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2276,10 +2276,10 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2417,10 +2417,10 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2558,10 +2558,10 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2699,10 +2699,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,13 +2804,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="M17" t="n">
-        <v>3.56</v>
+        <v>3.3</v>
       </c>
       <c r="N17" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2840,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,13 +2945,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2981,10 +2981,10 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.41</v>
+        <v>2.2</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3122,10 +3122,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,13 +3227,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>5.2</v>
+        <v>3.1</v>
       </c>
       <c r="M20" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>1.61</v>
+        <v>2.2</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3263,10 +3263,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.3</v>
+        <v>2.36</v>
       </c>
       <c r="M21" t="n">
-        <v>3.75</v>
+        <v>3.56</v>
       </c>
       <c r="N21" t="n">
-        <v>1.66</v>
+        <v>2.86</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3404,10 +3404,10 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
@@ -3473,22 +3473,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3545,10 +3545,10 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,52 +3650,52 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3</v>
+        <v>1.28</v>
       </c>
       <c r="M23" t="n">
-        <v>3.85</v>
+        <v>5.5</v>
       </c>
       <c r="N23" t="n">
+        <v>11</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Y23" t="n">
         <v>2.2</v>
       </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
       <c r="Z23" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.28</v>
+        <v>3</v>
       </c>
       <c r="M24" t="n">
-        <v>5.5</v>
+        <v>3.85</v>
       </c>
       <c r="N24" t="n">
-        <v>11</v>
+        <v>2.2</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Taiwan Taiwan Football Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Taichung Rock</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Taichung Futuro</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4178,22 +4178,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4397,10 +4397,10 @@
         <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.48</v>
+        <v>1.71</v>
       </c>
       <c r="M30" t="n">
-        <v>5</v>
+        <v>3.85</v>
       </c>
       <c r="N30" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4673,16 +4673,16 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
@@ -4742,22 +4742,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.25</v>
+        <v>2.39</v>
       </c>
       <c r="M31" t="n">
-        <v>3.75</v>
+        <v>2.85</v>
       </c>
       <c r="N31" t="n">
-        <v>2.01</v>
+        <v>3.2</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4883,22 +4883,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Taiwan Taiwan Football Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Taichung Rock</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Taichung Futuro</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5024,22 +5024,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Taiwan Taiwan Football Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Taipower</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>AC Taipei</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5060,13 +5060,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5096,10 +5096,10 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Taiwan Taiwan Football Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Taipower</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AC Taipei</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5342,13 +5342,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5447,7 +5447,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5660,10 +5660,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z37" t="n">
         <v>0</v>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5906,13 +5906,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5942,10 +5942,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -6021,12 +6021,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6047,13 +6047,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.6</v>
+        <v>1.85</v>
       </c>
       <c r="M40" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="N40" t="n">
-        <v>2.55</v>
+        <v>4.1</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -6083,16 +6083,16 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
         <v>0</v>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6611,13 +6611,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.85</v>
+        <v>2.6</v>
       </c>
       <c r="M44" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="N44" t="n">
-        <v>4.1</v>
+        <v>2.55</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6647,16 +6647,16 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB44" t="n">
         <v>0</v>
@@ -6857,22 +6857,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7034,13 +7034,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.53</v>
+        <v>3.74</v>
       </c>
       <c r="M47" t="n">
-        <v>4.75</v>
+        <v>3.9</v>
       </c>
       <c r="N47" t="n">
-        <v>5.35</v>
+        <v>1.89</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -7070,10 +7070,10 @@
         <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Z47" t="n">
         <v>0</v>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7290,12 +7290,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7316,13 +7316,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7598,13 +7598,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7739,13 +7739,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7844,22 +7844,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7916,10 +7916,10 @@
         <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
         <v>0</v>
@@ -7985,22 +7985,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8126,22 +8126,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Isloch</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Vitebsk</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Isloch</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vitebsk</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8972,22 +8972,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9008,13 +9008,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.58</v>
+        <v>4.9</v>
       </c>
       <c r="M61" t="n">
-        <v>4.2</v>
+        <v>4.34</v>
       </c>
       <c r="N61" t="n">
-        <v>5.5</v>
+        <v>1.62</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -9044,16 +9044,16 @@
         <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB61" t="n">
         <v>0</v>
@@ -9113,22 +9113,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -9149,13 +9149,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
         <v>0</v>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -9290,13 +9290,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -9326,10 +9326,10 @@
         <v>0</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z63" t="n">
         <v>0</v>
@@ -9818,22 +9818,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9854,13 +9854,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>6.21</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -10100,22 +10100,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -10136,13 +10136,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.59</v>
+        <v>1.46</v>
       </c>
       <c r="M69" t="n">
-        <v>3.54</v>
+        <v>4.65</v>
       </c>
       <c r="N69" t="n">
-        <v>2.59</v>
+        <v>6.21</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -10172,10 +10172,10 @@
         <v>0</v>
       </c>
       <c r="X69" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
         <v>0</v>
@@ -10241,7 +10241,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -10277,13 +10277,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -10313,10 +10313,10 @@
         <v>0</v>
       </c>
       <c r="X70" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z70" t="n">
         <v>0</v>
@@ -10523,7 +10523,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10805,7 +10805,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -11238,12 +11238,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>UN Käerjéng</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -11369,7 +11369,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>UNA Strassen</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -11661,12 +11661,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11802,12 +11802,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11933,7 +11933,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11943,12 +11943,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11965,7 +11965,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L82" t="n">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -12084,12 +12084,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -12215,22 +12215,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -12356,22 +12356,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -12497,7 +12497,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -12638,7 +12638,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -12648,12 +12648,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>UNA Strassen</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -12779,7 +12779,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -12789,12 +12789,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12920,7 +12920,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -12930,12 +12930,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -13061,7 +13061,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -13071,12 +13071,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>UN Käerjéng</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -13097,13 +13097,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -13202,22 +13202,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Slutsk</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Neman Grodno</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -13343,22 +13343,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Slutsk</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Neman Grodno</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -13375,7 +13375,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L92" t="n">
@@ -13484,7 +13484,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -13494,12 +13494,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -13520,13 +13520,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -13625,7 +13625,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -13635,12 +13635,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -13766,7 +13766,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -13917,12 +13917,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -14048,22 +14048,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -14340,12 +14340,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -14612,7 +14612,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -14622,12 +14622,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -14648,13 +14648,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -14684,10 +14684,10 @@
         <v>0</v>
       </c>
       <c r="X101" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z101" t="n">
         <v>0</v>
@@ -14753,22 +14753,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -14789,13 +14789,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -14825,10 +14825,10 @@
         <v>0</v>
       </c>
       <c r="X102" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
         <v>0</v>
@@ -14904,12 +14904,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -15317,7 +15317,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -15458,7 +15458,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -15468,12 +15468,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -15599,7 +15599,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -15609,12 +15609,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -15740,7 +15740,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -15750,12 +15750,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -15776,13 +15776,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -15812,10 +15812,10 @@
         <v>0</v>
       </c>
       <c r="X109" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Y109" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z109" t="n">
         <v>0</v>
@@ -15881,7 +15881,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -15891,12 +15891,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Komárno</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spartak Trnava</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -16022,7 +16022,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -16032,12 +16032,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -16054,7 +16054,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L111" t="n">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -16173,12 +16173,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -16304,7 +16304,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -16314,12 +16314,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -16336,7 +16336,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L113" t="n">
@@ -16445,7 +16445,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -16455,12 +16455,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ironi Ramat HaSharon</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -16481,13 +16481,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -16517,10 +16517,10 @@
         <v>0</v>
       </c>
       <c r="X114" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y114" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z114" t="n">
         <v>0</v>
@@ -16596,12 +16596,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -16727,7 +16727,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -16737,12 +16737,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -16759,7 +16759,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L116" t="n">
@@ -16868,7 +16868,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -16878,12 +16878,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -16904,13 +16904,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -16940,10 +16940,10 @@
         <v>0</v>
       </c>
       <c r="X117" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z117" t="n">
         <v>0</v>
@@ -17009,7 +17009,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -17019,12 +17019,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -17150,22 +17150,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -17301,12 +17301,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -17432,22 +17432,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -17573,7 +17573,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -17583,12 +17583,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Komárno</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Spartak Trnava</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -17609,13 +17609,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -17645,10 +17645,10 @@
         <v>0</v>
       </c>
       <c r="X122" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z122" t="n">
         <v>0</v>
@@ -17714,7 +17714,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -17724,12 +17724,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -17855,22 +17855,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -17891,13 +17891,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -17927,10 +17927,10 @@
         <v>0</v>
       </c>
       <c r="X124" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z124" t="n">
         <v>0</v>
@@ -17996,7 +17996,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -18006,12 +18006,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -18137,7 +18137,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -18147,12 +18147,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -18278,7 +18278,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -18288,12 +18288,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -18310,17 +18310,17 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -18350,10 +18350,10 @@
         <v>0</v>
       </c>
       <c r="X127" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z127" t="n">
         <v>0</v>
@@ -18419,7 +18419,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -18429,12 +18429,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -18451,7 +18451,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L128" t="n">
@@ -18560,7 +18560,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -18570,12 +18570,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -18701,7 +18701,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -18711,12 +18711,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -18842,7 +18842,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -18852,12 +18852,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -18983,22 +18983,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -19015,7 +19015,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L132" t="n">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -19265,7 +19265,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -19406,22 +19406,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -19547,22 +19547,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -19579,17 +19579,17 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M136" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -19829,7 +19829,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -19839,12 +19839,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -19980,12 +19980,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -20111,7 +20111,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -20121,12 +20121,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -20147,13 +20147,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -20183,10 +20183,10 @@
         <v>0</v>
       </c>
       <c r="X140" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y140" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z140" t="n">
         <v>0</v>
@@ -20252,7 +20252,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -20262,12 +20262,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -20288,13 +20288,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M141" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N141" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -20324,10 +20324,10 @@
         <v>0</v>
       </c>
       <c r="X141" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y141" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z141" t="n">
         <v>0</v>
@@ -20393,7 +20393,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -20403,12 +20403,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -20429,13 +20429,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M142" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -20465,10 +20465,10 @@
         <v>0</v>
       </c>
       <c r="X142" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Y142" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z142" t="n">
         <v>0</v>
@@ -20544,12 +20544,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -20675,7 +20675,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -20685,12 +20685,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -20816,7 +20816,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -20826,12 +20826,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -20957,7 +20957,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -20967,12 +20967,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -20993,13 +20993,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M146" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N146" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -21029,10 +21029,10 @@
         <v>0</v>
       </c>
       <c r="X146" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Y146" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z146" t="n">
         <v>0</v>
@@ -21098,7 +21098,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -21108,12 +21108,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -21239,7 +21239,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -21249,12 +21249,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -21380,7 +21380,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -21390,12 +21390,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Ironi Ramat HaSharon</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -21521,7 +21521,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -21531,12 +21531,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -21662,7 +21662,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -21672,12 +21672,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -21803,7 +21803,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -21813,12 +21813,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -21944,7 +21944,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -21954,12 +21954,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -21976,7 +21976,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L153" t="n">
@@ -22085,7 +22085,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -22095,12 +22095,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -22367,7 +22367,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -22377,12 +22377,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -22508,7 +22508,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -22518,12 +22518,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -22540,7 +22540,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L157" t="n">
@@ -22649,7 +22649,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -22659,12 +22659,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -22790,7 +22790,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -22800,12 +22800,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -22822,7 +22822,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L159" t="n">
@@ -23082,12 +23082,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -23108,13 +23108,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>2.11</v>
+        <v>3.64</v>
       </c>
       <c r="M161" t="n">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="N161" t="n">
-        <v>3.5</v>
+        <v>2.01</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -23144,10 +23144,10 @@
         <v>0</v>
       </c>
       <c r="X161" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="Y161" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="Z161" t="n">
         <v>0</v>
@@ -23223,12 +23223,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -23249,46 +23249,46 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>3.64</v>
+        <v>2.11</v>
       </c>
       <c r="M162" t="n">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="N162" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O162" t="n">
+        <v>0</v>
+      </c>
+      <c r="P162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>0</v>
+      </c>
+      <c r="R162" t="n">
+        <v>0</v>
+      </c>
+      <c r="S162" t="n">
+        <v>0</v>
+      </c>
+      <c r="T162" t="n">
+        <v>0</v>
+      </c>
+      <c r="U162" t="n">
+        <v>0</v>
+      </c>
+      <c r="V162" t="n">
+        <v>0</v>
+      </c>
+      <c r="W162" t="n">
+        <v>0</v>
+      </c>
+      <c r="X162" t="n">
         <v>2.01</v>
       </c>
-      <c r="O162" t="n">
-        <v>0</v>
-      </c>
-      <c r="P162" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
-      <c r="R162" t="n">
-        <v>0</v>
-      </c>
-      <c r="S162" t="n">
-        <v>0</v>
-      </c>
-      <c r="T162" t="n">
-        <v>0</v>
-      </c>
-      <c r="U162" t="n">
-        <v>0</v>
-      </c>
-      <c r="V162" t="n">
-        <v>0</v>
-      </c>
-      <c r="W162" t="n">
-        <v>0</v>
-      </c>
-      <c r="X162" t="n">
-        <v>1.95</v>
-      </c>
       <c r="Y162" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="Z162" t="n">
         <v>0</v>
@@ -23495,7 +23495,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -23505,12 +23505,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Primorje</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -23531,13 +23531,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M164" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N164" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -23567,10 +23567,10 @@
         <v>0</v>
       </c>
       <c r="X164" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Y164" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z164" t="n">
         <v>0</v>
@@ -23636,7 +23636,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -23646,12 +23646,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Primorje</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -23777,7 +23777,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -23787,12 +23787,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -23813,13 +23813,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N166" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -23849,10 +23849,10 @@
         <v>0</v>
       </c>
       <c r="X166" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y166" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z166" t="n">
         <v>0</v>
@@ -23918,7 +23918,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -23928,12 +23928,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -24059,7 +24059,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -24069,12 +24069,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -24095,13 +24095,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M168" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N168" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -24131,16 +24131,16 @@
         <v>0</v>
       </c>
       <c r="X168" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Y168" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z168" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA168" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB168" t="n">
         <v>0</v>
@@ -24200,7 +24200,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -24210,12 +24210,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -24236,13 +24236,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N169" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -24272,16 +24272,16 @@
         <v>0</v>
       </c>
       <c r="X169" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Y169" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z169" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA169" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB169" t="n">
         <v>0</v>
@@ -24341,7 +24341,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -24351,12 +24351,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -24482,7 +24482,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -24492,12 +24492,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -24518,13 +24518,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M171" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N171" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -24554,10 +24554,10 @@
         <v>0</v>
       </c>
       <c r="X171" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y171" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z171" t="n">
         <v>0</v>
@@ -24623,7 +24623,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -24633,12 +24633,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -24764,7 +24764,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -24774,12 +24774,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -24800,13 +24800,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M173" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N173" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -24836,10 +24836,10 @@
         <v>0</v>
       </c>
       <c r="X173" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Y173" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z173" t="n">
         <v>0</v>
@@ -25056,12 +25056,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -25187,7 +25187,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -25197,12 +25197,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -25328,7 +25328,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -25338,12 +25338,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -25469,7 +25469,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -25479,12 +25479,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -25610,22 +25610,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Dinamo Minsk</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -25892,22 +25892,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -26033,7 +26033,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -26043,12 +26043,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -26174,7 +26174,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -26184,12 +26184,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -26315,22 +26315,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -26607,12 +26607,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -26738,7 +26738,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -26748,12 +26748,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -26879,22 +26879,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -27020,22 +27020,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -27161,7 +27161,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -27171,12 +27171,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -27302,7 +27302,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -27312,12 +27312,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -27453,12 +27453,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -27594,12 +27594,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -27725,7 +27725,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -27735,12 +27735,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -27866,22 +27866,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -28007,22 +28007,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -28430,7 +28430,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -28440,12 +28440,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -28722,12 +28722,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -28853,22 +28853,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -29135,22 +29135,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Dinamo Minsk</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -29276,7 +29276,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -29286,12 +29286,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -29417,22 +29417,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -29558,7 +29558,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -29568,12 +29568,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -30122,7 +30122,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -30132,12 +30132,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -30158,13 +30158,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M211" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N211" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -30194,10 +30194,10 @@
         <v>0</v>
       </c>
       <c r="X211" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y211" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z211" t="n">
         <v>0</v>
@@ -30263,7 +30263,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -30273,12 +30273,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -30299,13 +30299,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M212" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N212" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -30335,10 +30335,10 @@
         <v>0</v>
       </c>
       <c r="X212" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Y212" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z212" t="n">
         <v>0</v>
@@ -30414,12 +30414,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -30440,13 +30440,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>2.55</v>
+        <v>3.15</v>
       </c>
       <c r="M213" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N213" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -30476,10 +30476,10 @@
         <v>0</v>
       </c>
       <c r="X213" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="Y213" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="Z213" t="n">
         <v>0</v>
@@ -30686,7 +30686,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -30696,12 +30696,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -30722,13 +30722,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M215" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N215" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -30837,12 +30837,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -31119,12 +31119,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -31250,22 +31250,22 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -31391,7 +31391,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -31401,12 +31401,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Podbrezová</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -31427,13 +31427,13 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M220" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N220" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -31532,7 +31532,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -31542,12 +31542,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Kolkheti Poti</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -31683,12 +31683,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -31814,22 +31814,22 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Kolkheti Poti</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -31850,13 +31850,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M223" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N223" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -31955,7 +31955,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -31965,12 +31965,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -32096,7 +32096,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -32106,12 +32106,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -32132,13 +32132,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M225" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N225" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -32237,7 +32237,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -32247,12 +32247,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -32378,7 +32378,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Podbrezová</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -32519,7 +32519,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -32529,12 +32529,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -32555,13 +32555,13 @@
         </is>
       </c>
       <c r="L228" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M228" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N228" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O228" t="n">
         <v>0</v>
@@ -32591,10 +32591,10 @@
         <v>0</v>
       </c>
       <c r="X228" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Y228" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Z228" t="n">
         <v>0</v>
@@ -32660,22 +32660,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -32696,13 +32696,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="M229" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N229" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -32738,10 +32738,10 @@
         <v>0</v>
       </c>
       <c r="Z229" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA229" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB229" t="n">
         <v>0</v>
@@ -32801,22 +32801,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -32837,13 +32837,13 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="M230" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N230" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O230" t="n">
         <v>0</v>
@@ -32879,10 +32879,10 @@
         <v>0</v>
       </c>
       <c r="Z230" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA230" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB230" t="n">
         <v>0</v>
@@ -32942,7 +32942,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -32952,12 +32952,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -32978,13 +32978,13 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M231" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N231" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O231" t="n">
         <v>0</v>
@@ -33014,10 +33014,10 @@
         <v>0</v>
       </c>
       <c r="X231" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Y231" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Z231" t="n">
         <v>0</v>
@@ -34211,22 +34211,22 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -34352,7 +34352,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -34362,12 +34362,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -34493,22 +34493,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -34634,7 +34634,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -34644,12 +34644,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -34775,7 +34775,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -34785,12 +34785,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -34916,22 +34916,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -35067,12 +35067,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -35349,12 +35349,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -35490,12 +35490,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -35621,22 +35621,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -35657,13 +35657,13 @@
         </is>
       </c>
       <c r="L250" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M250" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N250" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="O250" t="n">
         <v>0</v>
@@ -35693,10 +35693,10 @@
         <v>0</v>
       </c>
       <c r="X250" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y250" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z250" t="n">
         <v>0</v>
@@ -35762,22 +35762,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -35903,22 +35903,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -35939,13 +35939,13 @@
         </is>
       </c>
       <c r="L252" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M252" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N252" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="O252" t="n">
         <v>0</v>
@@ -35975,10 +35975,10 @@
         <v>0</v>
       </c>
       <c r="X252" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y252" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z252" t="n">
         <v>0</v>
@@ -36044,7 +36044,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -36054,12 +36054,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -36326,7 +36326,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -36336,12 +36336,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -36362,13 +36362,13 @@
         </is>
       </c>
       <c r="L255" t="n">
-        <v>2.85</v>
+        <v>1.43</v>
       </c>
       <c r="M255" t="n">
-        <v>3.45</v>
+        <v>4.7</v>
       </c>
       <c r="N255" t="n">
-        <v>2.38</v>
+        <v>7.3</v>
       </c>
       <c r="O255" t="n">
         <v>0</v>
@@ -36398,10 +36398,10 @@
         <v>0</v>
       </c>
       <c r="X255" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="Y255" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="Z255" t="n">
         <v>0</v>
@@ -36467,7 +36467,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -36477,12 +36477,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -36503,13 +36503,13 @@
         </is>
       </c>
       <c r="L256" t="n">
-        <v>1.43</v>
+        <v>2.85</v>
       </c>
       <c r="M256" t="n">
-        <v>4.7</v>
+        <v>3.45</v>
       </c>
       <c r="N256" t="n">
-        <v>7.3</v>
+        <v>2.38</v>
       </c>
       <c r="O256" t="n">
         <v>0</v>
@@ -36539,10 +36539,10 @@
         <v>0</v>
       </c>
       <c r="X256" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="Y256" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="Z256" t="n">
         <v>0</v>
@@ -36749,7 +36749,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -36759,12 +36759,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -36785,13 +36785,13 @@
         </is>
       </c>
       <c r="L258" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M258" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N258" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="O258" t="n">
         <v>0</v>
@@ -36890,22 +36890,22 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -37031,7 +37031,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -37041,12 +37041,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -37067,13 +37067,13 @@
         </is>
       </c>
       <c r="L260" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M260" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N260" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O260" t="n">
         <v>0</v>
@@ -37172,22 +37172,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -37313,7 +37313,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -37323,12 +37323,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -37349,13 +37349,13 @@
         </is>
       </c>
       <c r="L262" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M262" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N262" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O262" t="n">
         <v>0</v>
@@ -37379,16 +37379,16 @@
         <v>0</v>
       </c>
       <c r="V262" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W262" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="X262" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Y262" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z262" t="n">
         <v>0</v>
@@ -37454,7 +37454,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -37464,12 +37464,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -37490,13 +37490,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M263" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N263" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -37526,10 +37526,10 @@
         <v>0</v>
       </c>
       <c r="X263" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y263" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z263" t="n">
         <v>0</v>
@@ -37595,22 +37595,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -37631,13 +37631,13 @@
         </is>
       </c>
       <c r="L264" t="n">
-        <v>2.37</v>
+        <v>2.46</v>
       </c>
       <c r="M264" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="N264" t="n">
-        <v>3.07</v>
+        <v>2.8</v>
       </c>
       <c r="O264" t="n">
         <v>0</v>
@@ -37661,16 +37661,16 @@
         <v>0</v>
       </c>
       <c r="V264" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W264" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="X264" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y264" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z264" t="n">
         <v>0</v>
@@ -37746,12 +37746,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -37877,22 +37877,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -37913,13 +37913,13 @@
         </is>
       </c>
       <c r="L266" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M266" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N266" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O266" t="n">
         <v>0</v>
@@ -37949,10 +37949,10 @@
         <v>0</v>
       </c>
       <c r="X266" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y266" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z266" t="n">
         <v>0</v>
@@ -38028,12 +38028,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -38159,7 +38159,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -38169,12 +38169,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -38300,7 +38300,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -38310,12 +38310,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -38336,13 +38336,13 @@
         </is>
       </c>
       <c r="L269" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M269" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N269" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O269" t="n">
         <v>0</v>
@@ -38441,22 +38441,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -38582,22 +38582,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -38733,12 +38733,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -38864,7 +38864,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -38874,12 +38874,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -39005,7 +39005,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -39015,12 +39015,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -39041,13 +39041,13 @@
         </is>
       </c>
       <c r="L274" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M274" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N274" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O274" t="n">
         <v>0</v>
@@ -39077,10 +39077,10 @@
         <v>0</v>
       </c>
       <c r="X274" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Y274" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z274" t="n">
         <v>0</v>
@@ -39146,7 +39146,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -39156,12 +39156,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -39182,13 +39182,13 @@
         </is>
       </c>
       <c r="L275" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M275" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N275" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O275" t="n">
         <v>0</v>
@@ -39218,10 +39218,10 @@
         <v>0</v>
       </c>
       <c r="X275" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Y275" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z275" t="n">
         <v>0</v>
@@ -39569,7 +39569,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -39579,12 +39579,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -39605,13 +39605,13 @@
         </is>
       </c>
       <c r="L278" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M278" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N278" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O278" t="n">
         <v>0</v>
@@ -39641,10 +39641,10 @@
         <v>0</v>
       </c>
       <c r="X278" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Y278" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z278" t="n">
         <v>0</v>
@@ -39710,7 +39710,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -39720,12 +39720,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -39746,13 +39746,13 @@
         </is>
       </c>
       <c r="L279" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="M279" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N279" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O279" t="n">
         <v>0</v>
@@ -39782,10 +39782,10 @@
         <v>0</v>
       </c>
       <c r="X279" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Y279" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z279" t="n">
         <v>0</v>
@@ -39861,12 +39861,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -39887,13 +39887,13 @@
         </is>
       </c>
       <c r="L280" t="n">
-        <v>4.7</v>
+        <v>2.08</v>
       </c>
       <c r="M280" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N280" t="n">
         <v>3.55</v>
-      </c>
-      <c r="N280" t="n">
-        <v>1.71</v>
       </c>
       <c r="O280" t="n">
         <v>0</v>
@@ -40274,7 +40274,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -40284,12 +40284,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -40556,7 +40556,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -40566,12 +40566,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G285" t="n">

--- a/jogos_2025-08-24.xlsx
+++ b/jogos_2025-08-24.xlsx
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ming Chuan University</t>
+          <t>Tatung</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hang Yuen FC</t>
+          <t>Tainan City</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tatung</t>
+          <t>Ming Chuan University</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tainan City</t>
+          <t>Hang Yuen FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,13 +2945,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2981,10 +2981,10 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,13 +3227,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="M20" t="n">
-        <v>3.11</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3263,10 +3263,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -3332,22 +3332,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3404,10 +3404,10 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Taiwan Taiwan Football Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Taipower</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>AC Taipei</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5060,13 +5060,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -5096,10 +5096,10 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Taiwan Taiwan Football Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Taipower</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AC Taipei</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5201,13 +5201,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -5237,10 +5237,10 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z34" t="n">
         <v>0</v>
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5342,13 +5342,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.82</v>
+        <v>2.18</v>
       </c>
       <c r="M35" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N35" t="n">
-        <v>4.15</v>
+        <v>3.25</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5378,10 +5378,10 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2.03</v>
+        <v>2.18</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
@@ -8549,7 +8549,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8559,12 +8559,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8690,7 +8690,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9828,12 +9828,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -10277,13 +10277,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -10313,10 +10313,10 @@
         <v>0</v>
       </c>
       <c r="X70" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z70" t="n">
         <v>0</v>
@@ -10382,22 +10382,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -10418,13 +10418,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.13</v>
+        <v>1.46</v>
       </c>
       <c r="M71" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="N71" t="n">
-        <v>3.4</v>
+        <v>5.8</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -10454,16 +10454,16 @@
         <v>0</v>
       </c>
       <c r="X71" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB71" t="n">
         <v>0</v>
@@ -10523,22 +10523,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -10559,13 +10559,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.46</v>
+        <v>2.64</v>
       </c>
       <c r="M72" t="n">
-        <v>4.5</v>
+        <v>3.26</v>
       </c>
       <c r="N72" t="n">
-        <v>5.8</v>
+        <v>2.6</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -10595,16 +10595,16 @@
         <v>0</v>
       </c>
       <c r="X72" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z72" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
         <v>0</v>
@@ -10664,7 +10664,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -10674,12 +10674,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -10700,13 +10700,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -10736,10 +10736,10 @@
         <v>0</v>
       </c>
       <c r="X73" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
         <v>0</v>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.8</v>
+        <v>2.13</v>
       </c>
       <c r="M74" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N74" t="n">
-        <v>2.45</v>
+        <v>3.4</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10877,10 +10877,10 @@
         <v>0</v>
       </c>
       <c r="X74" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="Y74" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="Z74" t="n">
         <v>0</v>
@@ -11228,22 +11228,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>Slutsk</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Neman Grodno</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -11369,7 +11369,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -11379,12 +11379,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -11510,22 +11510,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Slutsk</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Neman Grodno</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -11661,12 +11661,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -11687,13 +11687,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -11723,10 +11723,10 @@
         <v>0</v>
       </c>
       <c r="X80" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z80" t="n">
         <v>0</v>
@@ -11792,7 +11792,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -11802,12 +11802,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -11933,7 +11933,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11943,12 +11943,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11969,13 +11969,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -12084,12 +12084,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -12110,13 +12110,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -12215,7 +12215,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -12497,22 +12497,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -12533,13 +12533,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -12569,10 +12569,10 @@
         <v>0</v>
       </c>
       <c r="X86" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z86" t="n">
         <v>0</v>
@@ -13343,22 +13343,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>UN Käerjéng</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -13484,22 +13484,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>UN Käerjéng</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -13625,22 +13625,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -13766,22 +13766,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13802,13 +13802,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -13844,10 +13844,10 @@
         <v>0</v>
       </c>
       <c r="Z95" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
         <v>0</v>
@@ -13907,22 +13907,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13943,13 +13943,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -13979,10 +13979,10 @@
         <v>0</v>
       </c>
       <c r="X96" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z96" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -14267,10 +14267,10 @@
         <v>0</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB98" t="n">
         <v>0</v>
@@ -14330,7 +14330,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -14340,12 +14340,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -14366,13 +14366,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -14402,10 +14402,10 @@
         <v>0</v>
       </c>
       <c r="X99" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z99" t="n">
         <v>0</v>
@@ -14481,12 +14481,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -14507,13 +14507,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.77</v>
+        <v>1.34</v>
       </c>
       <c r="M100" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="N100" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -14543,16 +14543,16 @@
         <v>0</v>
       </c>
       <c r="X100" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="Y100" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="Z100" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB100" t="n">
         <v>0</v>
@@ -14612,22 +14612,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -14648,13 +14648,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.95</v>
+        <v>2.85</v>
       </c>
       <c r="M101" t="n">
-        <v>3.53</v>
+        <v>3.9</v>
       </c>
       <c r="N101" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -14690,10 +14690,10 @@
         <v>0</v>
       </c>
       <c r="Z101" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AB101" t="n">
         <v>0</v>
@@ -14763,12 +14763,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -14789,13 +14789,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.34</v>
+        <v>3.7</v>
       </c>
       <c r="M102" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N102" t="n">
-        <v>6.6</v>
+        <v>2.02</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -14825,16 +14825,16 @@
         <v>0</v>
       </c>
       <c r="X102" t="n">
-        <v>1.6</v>
+        <v>2.07</v>
       </c>
       <c r="Y102" t="n">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="Z102" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
         <v>0</v>
@@ -14894,22 +14894,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -14930,13 +14930,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>3.7</v>
+        <v>2.05</v>
       </c>
       <c r="M103" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="N103" t="n">
-        <v>2.02</v>
+        <v>3.07</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -14966,10 +14966,10 @@
         <v>0</v>
       </c>
       <c r="X103" t="n">
-        <v>2.07</v>
+        <v>1.59</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.75</v>
+        <v>2.35</v>
       </c>
       <c r="Z103" t="n">
         <v>0</v>
@@ -18983,7 +18983,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -18993,12 +18993,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -19265,7 +19265,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -19547,7 +19547,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -19557,12 +19557,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -19688,7 +19688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -19698,12 +19698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -19839,12 +19839,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -19980,12 +19980,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -20111,7 +20111,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -20121,12 +20121,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -20262,12 +20262,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -20403,12 +20403,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -20534,7 +20534,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -20544,12 +20544,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -20685,12 +20685,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -20826,12 +20826,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -20848,17 +20848,17 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="M145" t="n">
-        <v>4.3</v>
+        <v>3.57</v>
       </c>
       <c r="N145" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -20888,16 +20888,16 @@
         <v>0</v>
       </c>
       <c r="X145" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="Y145" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Z145" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AA145" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB145" t="n">
         <v>0</v>
@@ -21098,7 +21098,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -21108,12 +21108,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -21239,22 +21239,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -21275,13 +21275,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M148" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="N148" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -21311,16 +21311,16 @@
         <v>0</v>
       </c>
       <c r="X148" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Y148" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z148" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AA148" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB148" t="n">
         <v>0</v>
@@ -21380,7 +21380,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -21390,12 +21390,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -21416,13 +21416,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M149" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N149" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -21531,12 +21531,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -21662,7 +21662,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -21672,12 +21672,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -21698,13 +21698,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M151" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -21813,12 +21813,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -21839,13 +21839,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M152" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -21854,43 +21854,43 @@
         <v>0</v>
       </c>
       <c r="Q152" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="R152" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S152" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T152" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U152" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="V152" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W152" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="X152" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y152" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z152" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA152" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB152" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC152" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD152" t="inlineStr">
         <is>
@@ -21903,19 +21903,19 @@
         </is>
       </c>
       <c r="AF152" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG152" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH152" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AI152" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ152" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AK152" t="n">
         <v>0</v>
@@ -21954,12 +21954,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -21980,13 +21980,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -21995,43 +21995,43 @@
         <v>0</v>
       </c>
       <c r="Q153" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="R153" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S153" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T153" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U153" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="V153" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W153" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="X153" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y153" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z153" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AB153" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC153" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD153" t="inlineStr">
         <is>
@@ -22044,19 +22044,19 @@
         </is>
       </c>
       <c r="AF153" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AG153" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH153" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AI153" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ153" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AK153" t="n">
         <v>0</v>
@@ -22085,7 +22085,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -22095,12 +22095,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -22121,13 +22121,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M154" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -22157,10 +22157,10 @@
         <v>0</v>
       </c>
       <c r="X154" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y154" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z154" t="n">
         <v>0</v>
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -22258,17 +22258,17 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L155" t="n">
-        <v>3.05</v>
+        <v>1.63</v>
       </c>
       <c r="M155" t="n">
-        <v>3.24</v>
+        <v>4.3</v>
       </c>
       <c r="N155" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -22298,10 +22298,10 @@
         <v>0</v>
       </c>
       <c r="X155" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Y155" t="n">
         <v>2.25</v>
-      </c>
-      <c r="Y155" t="n">
-        <v>1.65</v>
       </c>
       <c r="Z155" t="n">
         <v>0</v>
@@ -22377,12 +22377,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -30968,7 +30968,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -30978,12 +30978,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Podbrezová</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -31004,13 +31004,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M217" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="N217" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -31046,10 +31046,10 @@
         <v>0</v>
       </c>
       <c r="Z217" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA217" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB217" t="n">
         <v>0</v>
@@ -31109,7 +31109,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -31119,12 +31119,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -31145,13 +31145,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M218" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N218" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -31181,10 +31181,10 @@
         <v>0</v>
       </c>
       <c r="X218" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y218" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z218" t="n">
         <v>0</v>
@@ -31250,22 +31250,22 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Kolkheti Poti</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -31391,7 +31391,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -31401,12 +31401,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -31532,7 +31532,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -31542,12 +31542,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -31673,22 +31673,22 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Kolkheti Poti</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -31814,7 +31814,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -31824,12 +31824,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -31850,13 +31850,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M223" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N223" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -31886,10 +31886,10 @@
         <v>0</v>
       </c>
       <c r="X223" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y223" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z223" t="n">
         <v>0</v>
@@ -31955,22 +31955,22 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -31991,13 +31991,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M224" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N224" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -32033,10 +32033,10 @@
         <v>0</v>
       </c>
       <c r="Z224" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA224" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB224" t="n">
         <v>0</v>
@@ -32096,7 +32096,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -32106,12 +32106,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Podbrezová</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -32132,13 +32132,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M225" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="N225" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -32174,10 +32174,10 @@
         <v>0</v>
       </c>
       <c r="Z225" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA225" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB225" t="n">
         <v>0</v>
@@ -32247,12 +32247,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -32273,13 +32273,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M226" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N226" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -32315,10 +32315,10 @@
         <v>0</v>
       </c>
       <c r="Z226" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA226" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB226" t="n">
         <v>0</v>
@@ -32378,22 +32378,22 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -32414,13 +32414,13 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M227" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="N227" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -32450,10 +32450,10 @@
         <v>0</v>
       </c>
       <c r="X227" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y227" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z227" t="n">
         <v>0</v>
@@ -32660,7 +32660,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -32670,12 +32670,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -32696,13 +32696,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M229" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="N229" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -32732,10 +32732,10 @@
         <v>0</v>
       </c>
       <c r="X229" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y229" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z229" t="n">
         <v>0</v>
@@ -32801,22 +32801,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -32837,13 +32837,13 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="M230" t="n">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="N230" t="n">
-        <v>3.5</v>
+        <v>3.07</v>
       </c>
       <c r="O230" t="n">
         <v>0</v>
@@ -32873,10 +32873,10 @@
         <v>0</v>
       </c>
       <c r="X230" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="Y230" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="Z230" t="n">
         <v>0</v>
@@ -32942,7 +32942,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -32952,12 +32952,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -32978,13 +32978,13 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>1.21</v>
+        <v>6.9</v>
       </c>
       <c r="M231" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="N231" t="n">
-        <v>11</v>
+        <v>1.3</v>
       </c>
       <c r="O231" t="n">
         <v>0</v>
@@ -33014,16 +33014,16 @@
         <v>0</v>
       </c>
       <c r="X231" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Y231" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Z231" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA231" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB231" t="n">
         <v>0</v>
@@ -33083,22 +33083,22 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -33119,13 +33119,13 @@
         </is>
       </c>
       <c r="L232" t="n">
-        <v>6.9</v>
+        <v>1.8</v>
       </c>
       <c r="M232" t="n">
-        <v>4.8</v>
+        <v>3.58</v>
       </c>
       <c r="N232" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="O232" t="n">
         <v>0</v>
@@ -33155,16 +33155,16 @@
         <v>0</v>
       </c>
       <c r="X232" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Y232" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z232" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA232" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB232" t="n">
         <v>0</v>
@@ -33224,7 +33224,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -33234,12 +33234,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -33260,13 +33260,13 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>1.98</v>
+        <v>1.21</v>
       </c>
       <c r="M233" t="n">
-        <v>3.45</v>
+        <v>5.5</v>
       </c>
       <c r="N233" t="n">
-        <v>3.07</v>
+        <v>11</v>
       </c>
       <c r="O233" t="n">
         <v>0</v>
@@ -33296,10 +33296,10 @@
         <v>0</v>
       </c>
       <c r="X233" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="Y233" t="n">
-        <v>1.86</v>
+        <v>2.26</v>
       </c>
       <c r="Z233" t="n">
         <v>0</v>
